--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -6107,10 +6107,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119809202</v>
+        <v>119809044</v>
       </c>
       <c r="B48" t="n">
-        <v>78526</v>
+        <v>91852</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6119,38 +6119,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>403485</v>
+        <v>403399</v>
       </c>
       <c r="R48" t="n">
-        <v>6697329</v>
+        <v>6697339</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6197,22 +6197,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119809044</v>
+        <v>119809202</v>
       </c>
       <c r="B49" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6221,38 +6221,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>403399</v>
+        <v>403485</v>
       </c>
       <c r="R49" t="n">
-        <v>6697339</v>
+        <v>6697329</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6299,22 +6299,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119810170</v>
+        <v>119810050</v>
       </c>
       <c r="B50" t="n">
-        <v>78526</v>
+        <v>91832</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6327,34 +6327,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>403739</v>
+        <v>403566</v>
       </c>
       <c r="R50" t="n">
-        <v>6697375</v>
+        <v>6697312</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6413,7 +6413,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119808938</v>
+        <v>119810170</v>
       </c>
       <c r="B51" t="n">
         <v>78526</v>
@@ -6449,14 +6449,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>403325</v>
+        <v>403739</v>
       </c>
       <c r="R51" t="n">
-        <v>6697298</v>
+        <v>6697375</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6515,7 +6515,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119810449</v>
+        <v>119808938</v>
       </c>
       <c r="B52" t="n">
         <v>78526</v>
@@ -6551,14 +6551,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Långmyren, Långmyren, Vrm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>403791</v>
+        <v>403325</v>
       </c>
       <c r="R52" t="n">
-        <v>6697346</v>
+        <v>6697298</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6605,22 +6605,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119810050</v>
+        <v>119810449</v>
       </c>
       <c r="B53" t="n">
-        <v>91832</v>
+        <v>78526</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6633,34 +6633,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>403566</v>
+        <v>403791</v>
       </c>
       <c r="R53" t="n">
-        <v>6697312</v>
+        <v>6697346</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6707,12 +6707,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -5067,7 +5067,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119810264</v>
+        <v>119810437</v>
       </c>
       <c r="B38" t="n">
         <v>78526</v>
@@ -5103,14 +5103,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hallgruvkärret, Hallgruvkärret, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>403777</v>
+        <v>403805</v>
       </c>
       <c r="R38" t="n">
-        <v>6697344</v>
+        <v>6697361</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5157,19 +5157,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119810823</v>
+        <v>119809202</v>
       </c>
       <c r="B39" t="n">
         <v>78526</v>
@@ -5205,14 +5205,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>403887</v>
+        <v>403485</v>
       </c>
       <c r="R39" t="n">
-        <v>6697351</v>
+        <v>6697329</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5271,10 +5271,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119810619</v>
+        <v>119810651</v>
       </c>
       <c r="B40" t="n">
-        <v>74577</v>
+        <v>74630</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5283,25 +5283,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6426</v>
+        <v>308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119808909</v>
+        <v>119810356</v>
       </c>
       <c r="B41" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5385,38 +5385,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>403397</v>
+        <v>403789</v>
       </c>
       <c r="R41" t="n">
-        <v>6697336</v>
+        <v>6697379</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5463,19 +5463,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119808923</v>
+        <v>119810626</v>
       </c>
       <c r="B42" t="n">
         <v>78526</v>
@@ -5511,14 +5511,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>403354</v>
+        <v>403838</v>
       </c>
       <c r="R42" t="n">
-        <v>6697321</v>
+        <v>6697353</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119810057</v>
+        <v>119810145</v>
       </c>
       <c r="B43" t="n">
         <v>78526</v>
@@ -5613,14 +5613,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>403566</v>
+        <v>403722</v>
       </c>
       <c r="R43" t="n">
-        <v>6697312</v>
+        <v>6697347</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5667,22 +5667,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119809838</v>
+        <v>119810334</v>
       </c>
       <c r="B44" t="n">
-        <v>79567</v>
+        <v>78526</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5691,25 +5691,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>403506</v>
+        <v>403764</v>
       </c>
       <c r="R44" t="n">
-        <v>6697332</v>
+        <v>6697370</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5765,26 +5765,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5801,7 +5781,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119810431</v>
+        <v>119810380</v>
       </c>
       <c r="B45" t="n">
         <v>78526</v>
@@ -5841,10 +5821,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>403807</v>
+        <v>403769</v>
       </c>
       <c r="R45" t="n">
-        <v>6697384</v>
+        <v>6697386</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5903,7 +5883,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119810145</v>
+        <v>119808937</v>
       </c>
       <c r="B46" t="n">
         <v>78526</v>
@@ -5943,10 +5923,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>403722</v>
+        <v>403330</v>
       </c>
       <c r="R46" t="n">
-        <v>6697347</v>
+        <v>6697322</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6005,10 +5985,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119810179</v>
+        <v>119810375</v>
       </c>
       <c r="B47" t="n">
-        <v>74577</v>
+        <v>78526</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6017,38 +5997,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>403744</v>
+        <v>403786</v>
       </c>
       <c r="R47" t="n">
-        <v>6697356</v>
+        <v>6697381</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6095,22 +6075,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119809044</v>
+        <v>119810264</v>
       </c>
       <c r="B48" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6119,38 +6099,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Hallgruvkärret, Hallgruvkärret, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>403399</v>
+        <v>403777</v>
       </c>
       <c r="R48" t="n">
-        <v>6697339</v>
+        <v>6697344</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6197,19 +6177,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119809202</v>
+        <v>119809003</v>
       </c>
       <c r="B49" t="n">
         <v>78526</v>
@@ -6245,14 +6225,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>403485</v>
+        <v>403374</v>
       </c>
       <c r="R49" t="n">
-        <v>6697329</v>
+        <v>6697295</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6299,22 +6279,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119810050</v>
+        <v>119808919</v>
       </c>
       <c r="B50" t="n">
-        <v>91832</v>
+        <v>78526</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6327,34 +6307,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>403566</v>
+        <v>403384</v>
       </c>
       <c r="R50" t="n">
-        <v>6697312</v>
+        <v>6697323</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6401,22 +6381,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119810170</v>
+        <v>119810050</v>
       </c>
       <c r="B51" t="n">
-        <v>78526</v>
+        <v>91832</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6429,34 +6409,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>403739</v>
+        <v>403566</v>
       </c>
       <c r="R51" t="n">
-        <v>6697375</v>
+        <v>6697312</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6515,7 +6495,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119808938</v>
+        <v>119810449</v>
       </c>
       <c r="B52" t="n">
         <v>78526</v>
@@ -6551,14 +6531,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>403325</v>
+        <v>403791</v>
       </c>
       <c r="R52" t="n">
-        <v>6697298</v>
+        <v>6697346</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6605,19 +6585,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119810449</v>
+        <v>119810823</v>
       </c>
       <c r="B53" t="n">
         <v>78526</v>
@@ -6653,14 +6633,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>403791</v>
+        <v>403887</v>
       </c>
       <c r="R53" t="n">
-        <v>6697346</v>
+        <v>6697351</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6707,19 +6687,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119808924</v>
+        <v>119808930</v>
       </c>
       <c r="B54" t="n">
         <v>78526</v>
@@ -6759,10 +6739,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>403362</v>
+        <v>403363</v>
       </c>
       <c r="R54" t="n">
-        <v>6697324</v>
+        <v>6697334</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6821,7 +6801,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119808930</v>
+        <v>119810057</v>
       </c>
       <c r="B55" t="n">
         <v>78526</v>
@@ -6857,14 +6837,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>403363</v>
+        <v>403566</v>
       </c>
       <c r="R55" t="n">
-        <v>6697334</v>
+        <v>6697312</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6911,19 +6891,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119810334</v>
+        <v>119808938</v>
       </c>
       <c r="B56" t="n">
         <v>78526</v>
@@ -6959,14 +6939,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Långmyren, Långmyren, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>403764</v>
+        <v>403325</v>
       </c>
       <c r="R56" t="n">
-        <v>6697370</v>
+        <v>6697298</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7013,22 +6993,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119810396</v>
+        <v>119809326</v>
       </c>
       <c r="B57" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7041,34 +7021,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>403786</v>
+        <v>403487</v>
       </c>
       <c r="R57" t="n">
-        <v>6697381</v>
+        <v>6697326</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7127,7 +7107,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119810626</v>
+        <v>119810895</v>
       </c>
       <c r="B58" t="n">
         <v>78526</v>
@@ -7163,14 +7143,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>403838</v>
+        <v>403809</v>
       </c>
       <c r="R58" t="n">
-        <v>6697353</v>
+        <v>6697436</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7217,22 +7197,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119810223</v>
+        <v>119810088</v>
       </c>
       <c r="B59" t="n">
-        <v>78645</v>
+        <v>91884</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7241,38 +7221,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1036</v>
+        <v>5449</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hållav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Menegazzia terebrata</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>403752</v>
+        <v>403566</v>
       </c>
       <c r="R59" t="n">
-        <v>6697350</v>
+        <v>6697312</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7316,42 +7296,22 @@
       <c r="AG59" t="b">
         <v>0</v>
       </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Alnus glutinosa</t>
-        </is>
-      </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119810892</v>
+        <v>119810876</v>
       </c>
       <c r="B60" t="n">
         <v>78526</v>
@@ -7391,10 +7351,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>403853</v>
+        <v>403852</v>
       </c>
       <c r="R60" t="n">
-        <v>6697438</v>
+        <v>6697437</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7453,10 +7413,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119809028</v>
+        <v>119810179</v>
       </c>
       <c r="B61" t="n">
-        <v>78526</v>
+        <v>74577</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7465,25 +7425,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7493,10 +7453,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>403394</v>
+        <v>403744</v>
       </c>
       <c r="R61" t="n">
-        <v>6697322</v>
+        <v>6697356</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7555,7 +7515,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119810380</v>
+        <v>119809225</v>
       </c>
       <c r="B62" t="n">
         <v>78526</v>
@@ -7595,10 +7555,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>403769</v>
+        <v>403479</v>
       </c>
       <c r="R62" t="n">
-        <v>6697386</v>
+        <v>6697356</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7657,10 +7617,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119810356</v>
+        <v>119809838</v>
       </c>
       <c r="B63" t="n">
-        <v>78526</v>
+        <v>79567</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7669,38 +7629,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>403789</v>
+        <v>403506</v>
       </c>
       <c r="R63" t="n">
-        <v>6697379</v>
+        <v>6697332</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7744,22 +7704,42 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Betula</t>
+        </is>
+      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119810876</v>
+        <v>119810877</v>
       </c>
       <c r="B64" t="n">
         <v>78526</v>
@@ -7795,14 +7775,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>403852</v>
+        <v>403847</v>
       </c>
       <c r="R64" t="n">
-        <v>6697437</v>
+        <v>6697449</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7849,22 +7829,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119810088</v>
+        <v>119809124</v>
       </c>
       <c r="B65" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7877,34 +7857,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>403566</v>
+        <v>403456</v>
       </c>
       <c r="R65" t="n">
-        <v>6697312</v>
+        <v>6697335</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7951,19 +7931,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119809003</v>
+        <v>119810170</v>
       </c>
       <c r="B66" t="n">
         <v>78526</v>
@@ -7999,14 +7979,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>403374</v>
+        <v>403739</v>
       </c>
       <c r="R66" t="n">
-        <v>6697295</v>
+        <v>6697375</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8053,19 +8033,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119808919</v>
+        <v>119808923</v>
       </c>
       <c r="B67" t="n">
         <v>78526</v>
@@ -8101,14 +8081,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Långmyren, Långmyren, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>403384</v>
+        <v>403354</v>
       </c>
       <c r="R67" t="n">
-        <v>6697323</v>
+        <v>6697321</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8155,19 +8135,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119810604</v>
+        <v>119810431</v>
       </c>
       <c r="B68" t="n">
         <v>78526</v>
@@ -8203,14 +8183,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>403860</v>
+        <v>403807</v>
       </c>
       <c r="R68" t="n">
-        <v>6697352</v>
+        <v>6697384</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8257,22 +8237,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119810328</v>
+        <v>119808909</v>
       </c>
       <c r="B69" t="n">
-        <v>78526</v>
+        <v>91852</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8281,38 +8261,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>403792</v>
+        <v>403397</v>
       </c>
       <c r="R69" t="n">
-        <v>6697361</v>
+        <v>6697336</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8359,22 +8339,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119809326</v>
+        <v>119810892</v>
       </c>
       <c r="B70" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8387,34 +8367,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>403487</v>
+        <v>403853</v>
       </c>
       <c r="R70" t="n">
-        <v>6697326</v>
+        <v>6697438</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8473,10 +8453,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119810437</v>
+        <v>119810619</v>
       </c>
       <c r="B71" t="n">
-        <v>78526</v>
+        <v>74577</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8485,25 +8465,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8513,10 +8493,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>403805</v>
+        <v>403841</v>
       </c>
       <c r="R71" t="n">
-        <v>6697361</v>
+        <v>6697378</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8677,10 +8657,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119810895</v>
+        <v>119810223</v>
       </c>
       <c r="B73" t="n">
-        <v>78526</v>
+        <v>78645</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8689,25 +8669,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>1036</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Menegazzia terebrata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8717,10 +8697,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>403809</v>
+        <v>403752</v>
       </c>
       <c r="R73" t="n">
-        <v>6697436</v>
+        <v>6697350</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8763,6 +8743,26 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8779,7 +8779,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119810847</v>
+        <v>119810604</v>
       </c>
       <c r="B74" t="n">
         <v>78526</v>
@@ -8815,14 +8815,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>403886</v>
+        <v>403860</v>
       </c>
       <c r="R74" t="n">
-        <v>6697427</v>
+        <v>6697352</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8869,19 +8869,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119810877</v>
+        <v>119809028</v>
       </c>
       <c r="B75" t="n">
         <v>78526</v>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>403847</v>
+        <v>403394</v>
       </c>
       <c r="R75" t="n">
-        <v>6697449</v>
+        <v>6697322</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8983,7 +8983,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119810677</v>
+        <v>119808924</v>
       </c>
       <c r="B76" t="n">
         <v>78526</v>
@@ -9023,10 +9023,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>403862</v>
+        <v>403362</v>
       </c>
       <c r="R76" t="n">
-        <v>6697372</v>
+        <v>6697324</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9085,10 +9085,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119809225</v>
+        <v>119809044</v>
       </c>
       <c r="B77" t="n">
-        <v>78526</v>
+        <v>91852</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9097,25 +9097,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9125,10 +9125,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>403479</v>
+        <v>403399</v>
       </c>
       <c r="R77" t="n">
-        <v>6697356</v>
+        <v>6697339</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9187,7 +9187,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119808937</v>
+        <v>119810328</v>
       </c>
       <c r="B78" t="n">
         <v>78526</v>
@@ -9223,14 +9223,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>403330</v>
+        <v>403792</v>
       </c>
       <c r="R78" t="n">
-        <v>6697322</v>
+        <v>6697361</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9277,19 +9277,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119809124</v>
+        <v>119810847</v>
       </c>
       <c r="B79" t="n">
         <v>78526</v>
@@ -9329,10 +9329,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>403456</v>
+        <v>403886</v>
       </c>
       <c r="R79" t="n">
-        <v>6697335</v>
+        <v>6697427</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9391,10 +9391,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119810651</v>
+        <v>119810677</v>
       </c>
       <c r="B80" t="n">
-        <v>74630</v>
+        <v>78526</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9407,21 +9407,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9431,10 +9431,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>403841</v>
+        <v>403862</v>
       </c>
       <c r="R80" t="n">
-        <v>6697378</v>
+        <v>6697372</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -7005,10 +7005,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119809326</v>
+        <v>119810895</v>
       </c>
       <c r="B57" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7021,34 +7021,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>403487</v>
+        <v>403809</v>
       </c>
       <c r="R57" t="n">
-        <v>6697326</v>
+        <v>6697436</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7095,22 +7095,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119810895</v>
+        <v>119809326</v>
       </c>
       <c r="B58" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7123,34 +7123,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>403809</v>
+        <v>403487</v>
       </c>
       <c r="R58" t="n">
-        <v>6697436</v>
+        <v>6697326</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7197,12 +7197,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7617,10 +7617,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119809838</v>
+        <v>119810877</v>
       </c>
       <c r="B63" t="n">
-        <v>79567</v>
+        <v>78526</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7629,25 +7629,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7657,10 +7657,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>403506</v>
+        <v>403847</v>
       </c>
       <c r="R63" t="n">
-        <v>6697332</v>
+        <v>6697449</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7703,26 +7703,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7739,7 +7719,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119810877</v>
+        <v>119809124</v>
       </c>
       <c r="B64" t="n">
         <v>78526</v>
@@ -7779,10 +7759,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>403847</v>
+        <v>403456</v>
       </c>
       <c r="R64" t="n">
-        <v>6697449</v>
+        <v>6697335</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7841,10 +7821,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119809124</v>
+        <v>119809838</v>
       </c>
       <c r="B65" t="n">
-        <v>78526</v>
+        <v>79567</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7853,25 +7833,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7881,10 +7861,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>403456</v>
+        <v>403506</v>
       </c>
       <c r="R65" t="n">
-        <v>6697335</v>
+        <v>6697332</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7927,6 +7907,26 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8147,10 +8147,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119810431</v>
+        <v>119808909</v>
       </c>
       <c r="B68" t="n">
-        <v>78526</v>
+        <v>91852</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8159,25 +8159,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>403807</v>
+        <v>403397</v>
       </c>
       <c r="R68" t="n">
-        <v>6697384</v>
+        <v>6697336</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8249,10 +8249,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119808909</v>
+        <v>119810431</v>
       </c>
       <c r="B69" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8261,25 +8261,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8289,10 +8289,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>403397</v>
+        <v>403807</v>
       </c>
       <c r="R69" t="n">
-        <v>6697336</v>
+        <v>6697384</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8351,10 +8351,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119810892</v>
+        <v>119810619</v>
       </c>
       <c r="B70" t="n">
-        <v>78526</v>
+        <v>74577</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8363,38 +8363,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>403853</v>
+        <v>403841</v>
       </c>
       <c r="R70" t="n">
-        <v>6697438</v>
+        <v>6697378</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8441,22 +8441,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119810619</v>
+        <v>119810243</v>
       </c>
       <c r="B71" t="n">
-        <v>74577</v>
+        <v>78526</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8465,25 +8465,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>403841</v>
+        <v>403752</v>
       </c>
       <c r="R71" t="n">
-        <v>6697378</v>
+        <v>6697350</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8555,7 +8555,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119810243</v>
+        <v>119810892</v>
       </c>
       <c r="B72" t="n">
         <v>78526</v>
@@ -8591,14 +8591,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>403752</v>
+        <v>403853</v>
       </c>
       <c r="R72" t="n">
-        <v>6697350</v>
+        <v>6697438</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8645,12 +8645,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -9289,7 +9289,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119810847</v>
+        <v>119810677</v>
       </c>
       <c r="B79" t="n">
         <v>78526</v>
@@ -9329,10 +9329,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>403886</v>
+        <v>403862</v>
       </c>
       <c r="R79" t="n">
-        <v>6697427</v>
+        <v>6697372</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9391,7 +9391,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119810677</v>
+        <v>119810847</v>
       </c>
       <c r="B80" t="n">
         <v>78526</v>
@@ -9431,10 +9431,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>403862</v>
+        <v>403886</v>
       </c>
       <c r="R80" t="n">
-        <v>6697372</v>
+        <v>6697427</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -5067,7 +5067,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119810437</v>
+        <v>119810057</v>
       </c>
       <c r="B38" t="n">
         <v>78526</v>
@@ -5103,14 +5103,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>403805</v>
+        <v>403566</v>
       </c>
       <c r="R38" t="n">
-        <v>6697361</v>
+        <v>6697312</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5157,19 +5157,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119809202</v>
+        <v>119810431</v>
       </c>
       <c r="B39" t="n">
         <v>78526</v>
@@ -5205,14 +5205,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>403485</v>
+        <v>403807</v>
       </c>
       <c r="R39" t="n">
-        <v>6697329</v>
+        <v>6697384</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5259,22 +5259,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119810651</v>
+        <v>119810088</v>
       </c>
       <c r="B40" t="n">
-        <v>74630</v>
+        <v>91884</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5287,34 +5287,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>308</v>
+        <v>5449</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>403841</v>
+        <v>403566</v>
       </c>
       <c r="R40" t="n">
-        <v>6697378</v>
+        <v>6697312</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5361,19 +5361,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119810356</v>
+        <v>119810375</v>
       </c>
       <c r="B41" t="n">
         <v>78526</v>
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>403789</v>
+        <v>403786</v>
       </c>
       <c r="R41" t="n">
-        <v>6697379</v>
+        <v>6697381</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5475,7 +5475,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119810626</v>
+        <v>119810264</v>
       </c>
       <c r="B42" t="n">
         <v>78526</v>
@@ -5511,14 +5511,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Hallgruvkärret, Hallgruvkärret, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>403838</v>
+        <v>403777</v>
       </c>
       <c r="R42" t="n">
-        <v>6697353</v>
+        <v>6697344</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119810145</v>
+        <v>119810328</v>
       </c>
       <c r="B43" t="n">
         <v>78526</v>
@@ -5613,14 +5613,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>403722</v>
+        <v>403792</v>
       </c>
       <c r="R43" t="n">
-        <v>6697347</v>
+        <v>6697361</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5667,19 +5667,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119810334</v>
+        <v>119809124</v>
       </c>
       <c r="B44" t="n">
         <v>78526</v>
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>403764</v>
+        <v>403456</v>
       </c>
       <c r="R44" t="n">
-        <v>6697370</v>
+        <v>6697335</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5883,7 +5883,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119808937</v>
+        <v>119810356</v>
       </c>
       <c r="B46" t="n">
         <v>78526</v>
@@ -5919,14 +5919,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>403330</v>
+        <v>403789</v>
       </c>
       <c r="R46" t="n">
-        <v>6697322</v>
+        <v>6697379</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5973,19 +5973,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119810375</v>
+        <v>119809202</v>
       </c>
       <c r="B47" t="n">
         <v>78526</v>
@@ -6021,14 +6021,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>403786</v>
+        <v>403485</v>
       </c>
       <c r="R47" t="n">
-        <v>6697381</v>
+        <v>6697329</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6087,7 +6087,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119810264</v>
+        <v>119810823</v>
       </c>
       <c r="B48" t="n">
         <v>78526</v>
@@ -6123,14 +6123,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hallgruvkärret, Hallgruvkärret, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>403777</v>
+        <v>403887</v>
       </c>
       <c r="R48" t="n">
-        <v>6697344</v>
+        <v>6697351</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6189,7 +6189,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119809003</v>
+        <v>119810170</v>
       </c>
       <c r="B49" t="n">
         <v>78526</v>
@@ -6225,14 +6225,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>403374</v>
+        <v>403739</v>
       </c>
       <c r="R49" t="n">
-        <v>6697295</v>
+        <v>6697375</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6279,22 +6279,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119808919</v>
+        <v>119809326</v>
       </c>
       <c r="B50" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6307,34 +6307,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>403384</v>
+        <v>403487</v>
       </c>
       <c r="R50" t="n">
-        <v>6697323</v>
+        <v>6697326</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6381,22 +6381,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119810050</v>
+        <v>119808930</v>
       </c>
       <c r="B51" t="n">
-        <v>91832</v>
+        <v>78526</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6409,34 +6409,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>403566</v>
+        <v>403363</v>
       </c>
       <c r="R51" t="n">
-        <v>6697312</v>
+        <v>6697334</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6483,19 +6483,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119810449</v>
+        <v>119810334</v>
       </c>
       <c r="B52" t="n">
         <v>78526</v>
@@ -6535,10 +6535,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>403791</v>
+        <v>403764</v>
       </c>
       <c r="R52" t="n">
-        <v>6697346</v>
+        <v>6697370</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6597,7 +6597,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119810823</v>
+        <v>119808924</v>
       </c>
       <c r="B53" t="n">
         <v>78526</v>
@@ -6633,14 +6633,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>403887</v>
+        <v>403362</v>
       </c>
       <c r="R53" t="n">
-        <v>6697351</v>
+        <v>6697324</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6687,19 +6687,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119808930</v>
+        <v>119810626</v>
       </c>
       <c r="B54" t="n">
         <v>78526</v>
@@ -6735,14 +6735,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>403363</v>
+        <v>403838</v>
       </c>
       <c r="R54" t="n">
-        <v>6697334</v>
+        <v>6697353</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6789,19 +6789,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119810057</v>
+        <v>119810243</v>
       </c>
       <c r="B55" t="n">
         <v>78526</v>
@@ -6837,14 +6837,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>403566</v>
+        <v>403752</v>
       </c>
       <c r="R55" t="n">
-        <v>6697312</v>
+        <v>6697350</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6891,19 +6891,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119808938</v>
+        <v>119809028</v>
       </c>
       <c r="B56" t="n">
         <v>78526</v>
@@ -6939,14 +6939,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>403325</v>
+        <v>403394</v>
       </c>
       <c r="R56" t="n">
-        <v>6697298</v>
+        <v>6697322</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6993,22 +6993,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119810895</v>
+        <v>119810179</v>
       </c>
       <c r="B57" t="n">
-        <v>78526</v>
+        <v>74577</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7017,25 +7017,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7045,10 +7045,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>403809</v>
+        <v>403744</v>
       </c>
       <c r="R57" t="n">
-        <v>6697436</v>
+        <v>6697356</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7107,10 +7107,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119809326</v>
+        <v>119808938</v>
       </c>
       <c r="B58" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7123,34 +7123,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Långmyren, Långmyren, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>403487</v>
+        <v>403325</v>
       </c>
       <c r="R58" t="n">
-        <v>6697326</v>
+        <v>6697298</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7209,10 +7209,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119810088</v>
+        <v>119808919</v>
       </c>
       <c r="B59" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7225,34 +7225,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>403566</v>
+        <v>403384</v>
       </c>
       <c r="R59" t="n">
-        <v>6697312</v>
+        <v>6697323</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7299,19 +7299,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119810876</v>
+        <v>119810895</v>
       </c>
       <c r="B60" t="n">
         <v>78526</v>
@@ -7347,14 +7347,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>403852</v>
+        <v>403809</v>
       </c>
       <c r="R60" t="n">
-        <v>6697437</v>
+        <v>6697436</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7401,22 +7401,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119810179</v>
+        <v>119810449</v>
       </c>
       <c r="B61" t="n">
-        <v>74577</v>
+        <v>78526</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7425,25 +7425,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7453,10 +7453,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>403744</v>
+        <v>403791</v>
       </c>
       <c r="R61" t="n">
-        <v>6697356</v>
+        <v>6697346</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7515,10 +7515,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119809225</v>
+        <v>119810619</v>
       </c>
       <c r="B62" t="n">
-        <v>78526</v>
+        <v>74577</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7527,25 +7527,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7555,10 +7555,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>403479</v>
+        <v>403841</v>
       </c>
       <c r="R62" t="n">
-        <v>6697356</v>
+        <v>6697378</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7719,7 +7719,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119809124</v>
+        <v>119810876</v>
       </c>
       <c r="B64" t="n">
         <v>78526</v>
@@ -7755,14 +7755,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>403456</v>
+        <v>403852</v>
       </c>
       <c r="R64" t="n">
-        <v>6697335</v>
+        <v>6697437</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7809,22 +7809,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119809838</v>
+        <v>119810437</v>
       </c>
       <c r="B65" t="n">
-        <v>79567</v>
+        <v>78526</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7833,25 +7833,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7861,10 +7861,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>403506</v>
+        <v>403805</v>
       </c>
       <c r="R65" t="n">
-        <v>6697332</v>
+        <v>6697361</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7907,26 +7907,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7943,7 +7923,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119810170</v>
+        <v>119808937</v>
       </c>
       <c r="B66" t="n">
         <v>78526</v>
@@ -7979,14 +7959,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>403739</v>
+        <v>403330</v>
       </c>
       <c r="R66" t="n">
-        <v>6697375</v>
+        <v>6697322</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8033,19 +8013,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119808923</v>
+        <v>119810847</v>
       </c>
       <c r="B67" t="n">
         <v>78526</v>
@@ -8081,14 +8061,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>403354</v>
+        <v>403886</v>
       </c>
       <c r="R67" t="n">
-        <v>6697321</v>
+        <v>6697427</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8135,22 +8115,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119808909</v>
+        <v>119810223</v>
       </c>
       <c r="B68" t="n">
-        <v>91852</v>
+        <v>78645</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8159,25 +8139,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4366</v>
+        <v>1036</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Hållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Menegazzia terebrata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8187,10 +8167,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>403397</v>
+        <v>403752</v>
       </c>
       <c r="R68" t="n">
-        <v>6697336</v>
+        <v>6697350</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8233,6 +8213,26 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8249,10 +8249,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119810431</v>
+        <v>119809044</v>
       </c>
       <c r="B69" t="n">
-        <v>78526</v>
+        <v>91852</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8261,25 +8261,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8289,10 +8289,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>403807</v>
+        <v>403399</v>
       </c>
       <c r="R69" t="n">
-        <v>6697384</v>
+        <v>6697339</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8351,10 +8351,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119810619</v>
+        <v>119809838</v>
       </c>
       <c r="B70" t="n">
-        <v>74577</v>
+        <v>79567</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8367,21 +8367,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8391,10 +8391,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>403841</v>
+        <v>403506</v>
       </c>
       <c r="R70" t="n">
-        <v>6697378</v>
+        <v>6697332</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8437,6 +8437,26 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8453,10 +8473,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119810243</v>
+        <v>119810651</v>
       </c>
       <c r="B71" t="n">
-        <v>78526</v>
+        <v>74630</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8469,21 +8489,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8493,10 +8513,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>403752</v>
+        <v>403841</v>
       </c>
       <c r="R71" t="n">
-        <v>6697350</v>
+        <v>6697378</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8657,10 +8677,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119810223</v>
+        <v>119809003</v>
       </c>
       <c r="B73" t="n">
-        <v>78645</v>
+        <v>78526</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8669,25 +8689,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1036</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Hållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Menegazzia terebrata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8697,10 +8717,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>403752</v>
+        <v>403374</v>
       </c>
       <c r="R73" t="n">
-        <v>6697350</v>
+        <v>6697295</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8743,26 +8763,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8779,7 +8779,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119810604</v>
+        <v>119810145</v>
       </c>
       <c r="B74" t="n">
         <v>78526</v>
@@ -8815,14 +8815,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>403860</v>
+        <v>403722</v>
       </c>
       <c r="R74" t="n">
-        <v>6697352</v>
+        <v>6697347</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8869,19 +8869,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119809028</v>
+        <v>119810677</v>
       </c>
       <c r="B75" t="n">
         <v>78526</v>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>403394</v>
+        <v>403862</v>
       </c>
       <c r="R75" t="n">
-        <v>6697322</v>
+        <v>6697372</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8983,10 +8983,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119808924</v>
+        <v>119808909</v>
       </c>
       <c r="B76" t="n">
-        <v>78526</v>
+        <v>91852</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8995,25 +8995,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9023,10 +9023,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>403362</v>
+        <v>403397</v>
       </c>
       <c r="R76" t="n">
-        <v>6697324</v>
+        <v>6697336</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9085,10 +9085,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119809044</v>
+        <v>119810604</v>
       </c>
       <c r="B77" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9097,38 +9097,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>403399</v>
+        <v>403860</v>
       </c>
       <c r="R77" t="n">
-        <v>6697339</v>
+        <v>6697352</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9175,22 +9175,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119810328</v>
+        <v>119810050</v>
       </c>
       <c r="B78" t="n">
-        <v>78526</v>
+        <v>91832</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9203,34 +9203,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>403792</v>
+        <v>403566</v>
       </c>
       <c r="R78" t="n">
-        <v>6697361</v>
+        <v>6697312</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9289,7 +9289,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119810677</v>
+        <v>119808923</v>
       </c>
       <c r="B79" t="n">
         <v>78526</v>
@@ -9325,14 +9325,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Långmyren, Långmyren, Vrm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>403862</v>
+        <v>403354</v>
       </c>
       <c r="R79" t="n">
-        <v>6697372</v>
+        <v>6697321</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9379,19 +9379,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119810847</v>
+        <v>119809225</v>
       </c>
       <c r="B80" t="n">
         <v>78526</v>
@@ -9431,10 +9431,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>403886</v>
+        <v>403479</v>
       </c>
       <c r="R80" t="n">
-        <v>6697427</v>
+        <v>6697356</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -5067,10 +5067,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119810057</v>
+        <v>119810088</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5083,21 +5083,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5169,7 +5169,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119810431</v>
+        <v>119810057</v>
       </c>
       <c r="B39" t="n">
         <v>78526</v>
@@ -5205,14 +5205,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>403807</v>
+        <v>403566</v>
       </c>
       <c r="R39" t="n">
-        <v>6697384</v>
+        <v>6697312</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5259,22 +5259,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119810088</v>
+        <v>119810431</v>
       </c>
       <c r="B40" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5287,34 +5287,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>403566</v>
+        <v>403807</v>
       </c>
       <c r="R40" t="n">
-        <v>6697312</v>
+        <v>6697384</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5361,12 +5361,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119810328</v>
+        <v>119809124</v>
       </c>
       <c r="B43" t="n">
         <v>78526</v>
@@ -5613,14 +5613,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>403792</v>
+        <v>403456</v>
       </c>
       <c r="R43" t="n">
-        <v>6697361</v>
+        <v>6697335</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5667,19 +5667,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119809124</v>
+        <v>119810328</v>
       </c>
       <c r="B44" t="n">
         <v>78526</v>
@@ -5715,14 +5715,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>403456</v>
+        <v>403792</v>
       </c>
       <c r="R44" t="n">
-        <v>6697335</v>
+        <v>6697361</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5769,12 +5769,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -7719,7 +7719,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119810876</v>
+        <v>119808937</v>
       </c>
       <c r="B64" t="n">
         <v>78526</v>
@@ -7755,14 +7755,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>403852</v>
+        <v>403330</v>
       </c>
       <c r="R64" t="n">
-        <v>6697437</v>
+        <v>6697322</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7809,19 +7809,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119810437</v>
+        <v>119810876</v>
       </c>
       <c r="B65" t="n">
         <v>78526</v>
@@ -7857,14 +7857,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>403805</v>
+        <v>403852</v>
       </c>
       <c r="R65" t="n">
-        <v>6697361</v>
+        <v>6697437</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7911,19 +7911,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119808937</v>
+        <v>119810437</v>
       </c>
       <c r="B66" t="n">
         <v>78526</v>
@@ -7963,10 +7963,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>403330</v>
+        <v>403805</v>
       </c>
       <c r="R66" t="n">
-        <v>6697322</v>
+        <v>6697361</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8025,10 +8025,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119810847</v>
+        <v>119810223</v>
       </c>
       <c r="B67" t="n">
-        <v>78526</v>
+        <v>78645</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8037,25 +8037,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1036</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Menegazzia terebrata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8065,10 +8065,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>403886</v>
+        <v>403752</v>
       </c>
       <c r="R67" t="n">
-        <v>6697427</v>
+        <v>6697350</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8111,6 +8111,26 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8127,10 +8147,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119810223</v>
+        <v>119809044</v>
       </c>
       <c r="B68" t="n">
-        <v>78645</v>
+        <v>91852</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8139,25 +8159,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1036</v>
+        <v>4366</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hållav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Menegazzia terebrata</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8167,10 +8187,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>403752</v>
+        <v>403399</v>
       </c>
       <c r="R68" t="n">
-        <v>6697350</v>
+        <v>6697339</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8213,26 +8233,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8249,10 +8249,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119809044</v>
+        <v>119809838</v>
       </c>
       <c r="B69" t="n">
-        <v>91852</v>
+        <v>79567</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8265,21 +8265,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4366</v>
+        <v>229497</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8289,10 +8289,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>403399</v>
+        <v>403506</v>
       </c>
       <c r="R69" t="n">
-        <v>6697339</v>
+        <v>6697332</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8335,6 +8335,26 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8351,10 +8371,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119809838</v>
+        <v>119810847</v>
       </c>
       <c r="B70" t="n">
-        <v>79567</v>
+        <v>78526</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8363,25 +8383,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8391,10 +8411,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>403506</v>
+        <v>403886</v>
       </c>
       <c r="R70" t="n">
-        <v>6697332</v>
+        <v>6697427</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8437,26 +8457,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8881,10 +8881,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119810677</v>
+        <v>119808909</v>
       </c>
       <c r="B75" t="n">
-        <v>78526</v>
+        <v>91852</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8893,25 +8893,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>403862</v>
+        <v>403397</v>
       </c>
       <c r="R75" t="n">
-        <v>6697372</v>
+        <v>6697336</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8983,10 +8983,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119808909</v>
+        <v>119810677</v>
       </c>
       <c r="B76" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8995,25 +8995,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9023,10 +9023,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>403397</v>
+        <v>403862</v>
       </c>
       <c r="R76" t="n">
-        <v>6697336</v>
+        <v>6697372</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -5067,10 +5067,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119810088</v>
+        <v>119810892</v>
       </c>
       <c r="B38" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5083,34 +5083,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>403566</v>
+        <v>403853</v>
       </c>
       <c r="R38" t="n">
-        <v>6697312</v>
+        <v>6697438</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5169,10 +5169,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119810057</v>
+        <v>119808909</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>91852</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5181,38 +5181,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>403566</v>
+        <v>403397</v>
       </c>
       <c r="R39" t="n">
-        <v>6697312</v>
+        <v>6697336</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5259,19 +5259,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119810431</v>
+        <v>119810877</v>
       </c>
       <c r="B40" t="n">
         <v>78526</v>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>403807</v>
+        <v>403847</v>
       </c>
       <c r="R40" t="n">
-        <v>6697384</v>
+        <v>6697449</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5373,7 +5373,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119810375</v>
+        <v>119810823</v>
       </c>
       <c r="B41" t="n">
         <v>78526</v>
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>403786</v>
+        <v>403887</v>
       </c>
       <c r="R41" t="n">
-        <v>6697381</v>
+        <v>6697351</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5475,7 +5475,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119810264</v>
+        <v>119810243</v>
       </c>
       <c r="B42" t="n">
         <v>78526</v>
@@ -5511,14 +5511,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hallgruvkärret, Hallgruvkärret, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>403777</v>
+        <v>403752</v>
       </c>
       <c r="R42" t="n">
-        <v>6697344</v>
+        <v>6697350</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5565,19 +5565,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119809124</v>
+        <v>119810057</v>
       </c>
       <c r="B43" t="n">
         <v>78526</v>
@@ -5613,14 +5613,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>403456</v>
+        <v>403566</v>
       </c>
       <c r="R43" t="n">
-        <v>6697335</v>
+        <v>6697312</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5667,19 +5667,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119810328</v>
+        <v>119810170</v>
       </c>
       <c r="B44" t="n">
         <v>78526</v>
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>403792</v>
+        <v>403739</v>
       </c>
       <c r="R44" t="n">
-        <v>6697361</v>
+        <v>6697375</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5781,7 +5781,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119810380</v>
+        <v>119810334</v>
       </c>
       <c r="B45" t="n">
         <v>78526</v>
@@ -5821,10 +5821,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>403769</v>
+        <v>403764</v>
       </c>
       <c r="R45" t="n">
-        <v>6697386</v>
+        <v>6697370</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5883,7 +5883,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119810356</v>
+        <v>119810449</v>
       </c>
       <c r="B46" t="n">
         <v>78526</v>
@@ -5919,14 +5919,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>403789</v>
+        <v>403791</v>
       </c>
       <c r="R46" t="n">
-        <v>6697379</v>
+        <v>6697346</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5973,22 +5973,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119809202</v>
+        <v>119810223</v>
       </c>
       <c r="B47" t="n">
-        <v>78526</v>
+        <v>78645</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5997,38 +5997,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1036</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Menegazzia terebrata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>403485</v>
+        <v>403752</v>
       </c>
       <c r="R47" t="n">
-        <v>6697329</v>
+        <v>6697350</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6072,22 +6072,42 @@
       <c r="AG47" t="b">
         <v>0</v>
       </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Alnus glutinosa</t>
+        </is>
+      </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119810823</v>
+        <v>119810435</v>
       </c>
       <c r="B48" t="n">
         <v>78526</v>
@@ -6127,10 +6147,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>403887</v>
+        <v>403786</v>
       </c>
       <c r="R48" t="n">
-        <v>6697351</v>
+        <v>6697381</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6189,7 +6209,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119810170</v>
+        <v>119810380</v>
       </c>
       <c r="B49" t="n">
         <v>78526</v>
@@ -6225,14 +6245,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>403739</v>
+        <v>403769</v>
       </c>
       <c r="R49" t="n">
-        <v>6697375</v>
+        <v>6697386</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6279,22 +6299,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119809326</v>
+        <v>119810437</v>
       </c>
       <c r="B50" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6307,34 +6327,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>403487</v>
+        <v>403805</v>
       </c>
       <c r="R50" t="n">
-        <v>6697326</v>
+        <v>6697361</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6381,19 +6401,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119808930</v>
+        <v>119810876</v>
       </c>
       <c r="B51" t="n">
         <v>78526</v>
@@ -6429,14 +6449,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>403363</v>
+        <v>403852</v>
       </c>
       <c r="R51" t="n">
-        <v>6697334</v>
+        <v>6697437</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6483,19 +6503,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119810334</v>
+        <v>119809003</v>
       </c>
       <c r="B52" t="n">
         <v>78526</v>
@@ -6535,10 +6555,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>403764</v>
+        <v>403374</v>
       </c>
       <c r="R52" t="n">
-        <v>6697370</v>
+        <v>6697295</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6597,10 +6617,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119808924</v>
+        <v>119810050</v>
       </c>
       <c r="B53" t="n">
-        <v>78526</v>
+        <v>91832</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6613,34 +6633,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>403362</v>
+        <v>403566</v>
       </c>
       <c r="R53" t="n">
-        <v>6697324</v>
+        <v>6697312</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6687,19 +6707,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119810626</v>
+        <v>119810847</v>
       </c>
       <c r="B54" t="n">
         <v>78526</v>
@@ -6735,14 +6755,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>403838</v>
+        <v>403886</v>
       </c>
       <c r="R54" t="n">
-        <v>6697353</v>
+        <v>6697427</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6789,19 +6809,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119810243</v>
+        <v>119809124</v>
       </c>
       <c r="B55" t="n">
         <v>78526</v>
@@ -6841,10 +6861,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>403752</v>
+        <v>403456</v>
       </c>
       <c r="R55" t="n">
-        <v>6697350</v>
+        <v>6697335</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6903,7 +6923,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119809028</v>
+        <v>119810356</v>
       </c>
       <c r="B56" t="n">
         <v>78526</v>
@@ -6939,14 +6959,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>403394</v>
+        <v>403789</v>
       </c>
       <c r="R56" t="n">
-        <v>6697322</v>
+        <v>6697379</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6993,22 +7013,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119810179</v>
+        <v>119810328</v>
       </c>
       <c r="B57" t="n">
-        <v>74577</v>
+        <v>78526</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7017,38 +7037,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>403744</v>
+        <v>403792</v>
       </c>
       <c r="R57" t="n">
-        <v>6697356</v>
+        <v>6697361</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7095,19 +7115,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119808938</v>
+        <v>119808930</v>
       </c>
       <c r="B58" t="n">
         <v>78526</v>
@@ -7143,14 +7163,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>403325</v>
+        <v>403363</v>
       </c>
       <c r="R58" t="n">
-        <v>6697298</v>
+        <v>6697334</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7197,19 +7217,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119808919</v>
+        <v>119809225</v>
       </c>
       <c r="B59" t="n">
         <v>78526</v>
@@ -7249,10 +7269,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>403384</v>
+        <v>403479</v>
       </c>
       <c r="R59" t="n">
-        <v>6697323</v>
+        <v>6697356</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7311,10 +7331,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119810895</v>
+        <v>119810088</v>
       </c>
       <c r="B60" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7327,34 +7347,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>403809</v>
+        <v>403566</v>
       </c>
       <c r="R60" t="n">
-        <v>6697436</v>
+        <v>6697312</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7401,19 +7421,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119810449</v>
+        <v>119809028</v>
       </c>
       <c r="B61" t="n">
         <v>78526</v>
@@ -7453,10 +7473,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>403791</v>
+        <v>403394</v>
       </c>
       <c r="R61" t="n">
-        <v>6697346</v>
+        <v>6697322</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7515,10 +7535,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119810619</v>
+        <v>119809202</v>
       </c>
       <c r="B62" t="n">
-        <v>74577</v>
+        <v>78526</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7527,38 +7547,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>403841</v>
+        <v>403485</v>
       </c>
       <c r="R62" t="n">
-        <v>6697378</v>
+        <v>6697329</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7605,22 +7625,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119810877</v>
+        <v>119809326</v>
       </c>
       <c r="B63" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7633,34 +7653,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>403847</v>
+        <v>403487</v>
       </c>
       <c r="R63" t="n">
-        <v>6697449</v>
+        <v>6697326</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7707,22 +7727,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119808937</v>
+        <v>119809044</v>
       </c>
       <c r="B64" t="n">
-        <v>78526</v>
+        <v>91852</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7731,25 +7751,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7759,10 +7779,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>403330</v>
+        <v>403399</v>
       </c>
       <c r="R64" t="n">
-        <v>6697322</v>
+        <v>6697339</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7821,7 +7841,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119810876</v>
+        <v>119808923</v>
       </c>
       <c r="B65" t="n">
         <v>78526</v>
@@ -7857,14 +7877,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Långmyren, Långmyren, Vrm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>403852</v>
+        <v>403354</v>
       </c>
       <c r="R65" t="n">
-        <v>6697437</v>
+        <v>6697321</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7923,7 +7943,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119810437</v>
+        <v>119808919</v>
       </c>
       <c r="B66" t="n">
         <v>78526</v>
@@ -7963,10 +7983,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>403805</v>
+        <v>403384</v>
       </c>
       <c r="R66" t="n">
-        <v>6697361</v>
+        <v>6697323</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8025,10 +8045,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119810223</v>
+        <v>119810145</v>
       </c>
       <c r="B67" t="n">
-        <v>78645</v>
+        <v>78526</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8037,25 +8057,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1036</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Menegazzia terebrata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8065,10 +8085,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>403752</v>
+        <v>403722</v>
       </c>
       <c r="R67" t="n">
-        <v>6697350</v>
+        <v>6697347</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8111,26 +8131,6 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8147,10 +8147,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119809044</v>
+        <v>119810677</v>
       </c>
       <c r="B68" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8159,25 +8159,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>403399</v>
+        <v>403862</v>
       </c>
       <c r="R68" t="n">
-        <v>6697339</v>
+        <v>6697372</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8249,10 +8249,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119809838</v>
+        <v>119810651</v>
       </c>
       <c r="B69" t="n">
-        <v>79567</v>
+        <v>74630</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8261,25 +8261,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229497</v>
+        <v>308</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8289,10 +8289,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>403506</v>
+        <v>403841</v>
       </c>
       <c r="R69" t="n">
-        <v>6697332</v>
+        <v>6697378</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8335,26 +8335,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8371,7 +8351,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119810847</v>
+        <v>119810264</v>
       </c>
       <c r="B70" t="n">
         <v>78526</v>
@@ -8407,14 +8387,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Hallgruvkärret, Hallgruvkärret, Vrm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>403886</v>
+        <v>403777</v>
       </c>
       <c r="R70" t="n">
-        <v>6697427</v>
+        <v>6697344</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8461,22 +8441,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119810651</v>
+        <v>119810619</v>
       </c>
       <c r="B71" t="n">
-        <v>74630</v>
+        <v>74577</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8485,25 +8465,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>308</v>
+        <v>6426</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8575,10 +8555,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119810892</v>
+        <v>119809838</v>
       </c>
       <c r="B72" t="n">
-        <v>78526</v>
+        <v>79567</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8587,38 +8567,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>403853</v>
+        <v>403506</v>
       </c>
       <c r="R72" t="n">
-        <v>6697438</v>
+        <v>6697332</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8662,22 +8642,42 @@
       <c r="AG72" t="b">
         <v>0</v>
       </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Betula</t>
+        </is>
+      </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119809003</v>
+        <v>119810626</v>
       </c>
       <c r="B73" t="n">
         <v>78526</v>
@@ -8713,14 +8713,14 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>403374</v>
+        <v>403838</v>
       </c>
       <c r="R73" t="n">
-        <v>6697295</v>
+        <v>6697353</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8767,19 +8767,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119810145</v>
+        <v>119808938</v>
       </c>
       <c r="B74" t="n">
         <v>78526</v>
@@ -8815,14 +8815,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Långmyren, Långmyren, Vrm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>403722</v>
+        <v>403325</v>
       </c>
       <c r="R74" t="n">
-        <v>6697347</v>
+        <v>6697298</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8869,22 +8869,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119808909</v>
+        <v>119810179</v>
       </c>
       <c r="B75" t="n">
-        <v>91852</v>
+        <v>74577</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8897,21 +8897,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4366</v>
+        <v>6426</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>403397</v>
+        <v>403744</v>
       </c>
       <c r="R75" t="n">
-        <v>6697336</v>
+        <v>6697356</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8983,7 +8983,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119810677</v>
+        <v>119810431</v>
       </c>
       <c r="B76" t="n">
         <v>78526</v>
@@ -9023,10 +9023,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>403862</v>
+        <v>403807</v>
       </c>
       <c r="R76" t="n">
-        <v>6697372</v>
+        <v>6697384</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9085,7 +9085,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119810604</v>
+        <v>119808937</v>
       </c>
       <c r="B77" t="n">
         <v>78526</v>
@@ -9121,14 +9121,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>403860</v>
+        <v>403330</v>
       </c>
       <c r="R77" t="n">
-        <v>6697352</v>
+        <v>6697322</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9175,22 +9175,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119810050</v>
+        <v>119810604</v>
       </c>
       <c r="B78" t="n">
-        <v>91832</v>
+        <v>78526</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9203,34 +9203,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>403566</v>
+        <v>403860</v>
       </c>
       <c r="R78" t="n">
-        <v>6697312</v>
+        <v>6697352</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9289,7 +9289,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119808923</v>
+        <v>119810895</v>
       </c>
       <c r="B79" t="n">
         <v>78526</v>
@@ -9325,14 +9325,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>403354</v>
+        <v>403809</v>
       </c>
       <c r="R79" t="n">
-        <v>6697321</v>
+        <v>6697436</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9379,19 +9379,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119809225</v>
+        <v>119808924</v>
       </c>
       <c r="B80" t="n">
         <v>78526</v>
@@ -9431,10 +9431,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>403479</v>
+        <v>403362</v>
       </c>
       <c r="R80" t="n">
-        <v>6697356</v>
+        <v>6697324</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -5985,10 +5985,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119810223</v>
+        <v>119810380</v>
       </c>
       <c r="B47" t="n">
-        <v>78645</v>
+        <v>78526</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5997,25 +5997,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1036</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Menegazzia terebrata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>403752</v>
+        <v>403769</v>
       </c>
       <c r="R47" t="n">
-        <v>6697350</v>
+        <v>6697386</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6071,26 +6071,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6107,7 +6087,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119810435</v>
+        <v>119810437</v>
       </c>
       <c r="B48" t="n">
         <v>78526</v>
@@ -6143,14 +6123,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>403786</v>
+        <v>403805</v>
       </c>
       <c r="R48" t="n">
-        <v>6697381</v>
+        <v>6697361</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6197,22 +6177,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119810380</v>
+        <v>119810223</v>
       </c>
       <c r="B49" t="n">
-        <v>78526</v>
+        <v>78645</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6221,25 +6201,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1036</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Menegazzia terebrata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6249,10 +6229,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>403769</v>
+        <v>403752</v>
       </c>
       <c r="R49" t="n">
-        <v>6697386</v>
+        <v>6697350</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6295,6 +6275,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6311,7 +6311,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119810437</v>
+        <v>119810435</v>
       </c>
       <c r="B50" t="n">
         <v>78526</v>
@@ -6347,14 +6347,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>403805</v>
+        <v>403786</v>
       </c>
       <c r="R50" t="n">
-        <v>6697361</v>
+        <v>6697381</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6401,12 +6401,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6515,10 +6515,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119809003</v>
+        <v>119810050</v>
       </c>
       <c r="B52" t="n">
-        <v>78526</v>
+        <v>91832</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6531,34 +6531,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>403374</v>
+        <v>403566</v>
       </c>
       <c r="R52" t="n">
-        <v>6697295</v>
+        <v>6697312</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6605,22 +6605,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119810050</v>
+        <v>119809003</v>
       </c>
       <c r="B53" t="n">
-        <v>91832</v>
+        <v>78526</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6633,34 +6633,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>403566</v>
+        <v>403374</v>
       </c>
       <c r="R53" t="n">
-        <v>6697312</v>
+        <v>6697295</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6707,19 +6707,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119810847</v>
+        <v>119809124</v>
       </c>
       <c r="B54" t="n">
         <v>78526</v>
@@ -6759,10 +6759,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>403886</v>
+        <v>403456</v>
       </c>
       <c r="R54" t="n">
-        <v>6697427</v>
+        <v>6697335</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6821,7 +6821,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119809124</v>
+        <v>119810356</v>
       </c>
       <c r="B55" t="n">
         <v>78526</v>
@@ -6857,14 +6857,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>403456</v>
+        <v>403789</v>
       </c>
       <c r="R55" t="n">
-        <v>6697335</v>
+        <v>6697379</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6911,19 +6911,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119810356</v>
+        <v>119810328</v>
       </c>
       <c r="B56" t="n">
         <v>78526</v>
@@ -6963,10 +6963,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>403789</v>
+        <v>403792</v>
       </c>
       <c r="R56" t="n">
-        <v>6697379</v>
+        <v>6697361</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7025,7 +7025,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119810328</v>
+        <v>119810847</v>
       </c>
       <c r="B57" t="n">
         <v>78526</v>
@@ -7061,14 +7061,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>403792</v>
+        <v>403886</v>
       </c>
       <c r="R57" t="n">
-        <v>6697361</v>
+        <v>6697427</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7115,12 +7115,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7841,7 +7841,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119808923</v>
+        <v>119808919</v>
       </c>
       <c r="B65" t="n">
         <v>78526</v>
@@ -7877,14 +7877,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>403354</v>
+        <v>403384</v>
       </c>
       <c r="R65" t="n">
-        <v>6697321</v>
+        <v>6697323</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7931,19 +7931,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119808919</v>
+        <v>119810145</v>
       </c>
       <c r="B66" t="n">
         <v>78526</v>
@@ -7983,10 +7983,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>403384</v>
+        <v>403722</v>
       </c>
       <c r="R66" t="n">
-        <v>6697323</v>
+        <v>6697347</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8045,7 +8045,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119810145</v>
+        <v>119808923</v>
       </c>
       <c r="B67" t="n">
         <v>78526</v>
@@ -8081,14 +8081,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Långmyren, Långmyren, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>403722</v>
+        <v>403354</v>
       </c>
       <c r="R67" t="n">
-        <v>6697347</v>
+        <v>6697321</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8135,12 +8135,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -5475,7 +5475,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119810243</v>
+        <v>119810057</v>
       </c>
       <c r="B42" t="n">
         <v>78526</v>
@@ -5511,14 +5511,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>403752</v>
+        <v>403566</v>
       </c>
       <c r="R42" t="n">
-        <v>6697350</v>
+        <v>6697312</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5565,19 +5565,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119810057</v>
+        <v>119810170</v>
       </c>
       <c r="B43" t="n">
         <v>78526</v>
@@ -5613,14 +5613,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>403566</v>
+        <v>403739</v>
       </c>
       <c r="R43" t="n">
-        <v>6697312</v>
+        <v>6697375</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5679,7 +5679,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119810170</v>
+        <v>119810334</v>
       </c>
       <c r="B44" t="n">
         <v>78526</v>
@@ -5715,14 +5715,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>403739</v>
+        <v>403764</v>
       </c>
       <c r="R44" t="n">
-        <v>6697375</v>
+        <v>6697370</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5769,19 +5769,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119810334</v>
+        <v>119810449</v>
       </c>
       <c r="B45" t="n">
         <v>78526</v>
@@ -5821,10 +5821,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>403764</v>
+        <v>403791</v>
       </c>
       <c r="R45" t="n">
-        <v>6697370</v>
+        <v>6697346</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5883,7 +5883,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119810449</v>
+        <v>119810243</v>
       </c>
       <c r="B46" t="n">
         <v>78526</v>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>403791</v>
+        <v>403752</v>
       </c>
       <c r="R46" t="n">
-        <v>6697346</v>
+        <v>6697350</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5985,10 +5985,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119810380</v>
+        <v>119810223</v>
       </c>
       <c r="B47" t="n">
-        <v>78526</v>
+        <v>78645</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5997,25 +5997,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1036</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Menegazzia terebrata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>403769</v>
+        <v>403752</v>
       </c>
       <c r="R47" t="n">
-        <v>6697386</v>
+        <v>6697350</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6071,6 +6071,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6087,7 +6107,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119810437</v>
+        <v>119810435</v>
       </c>
       <c r="B48" t="n">
         <v>78526</v>
@@ -6123,14 +6143,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>403805</v>
+        <v>403786</v>
       </c>
       <c r="R48" t="n">
-        <v>6697361</v>
+        <v>6697381</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6177,22 +6197,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119810223</v>
+        <v>119810380</v>
       </c>
       <c r="B49" t="n">
-        <v>78645</v>
+        <v>78526</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6201,25 +6221,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1036</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Menegazzia terebrata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6229,10 +6249,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>403752</v>
+        <v>403769</v>
       </c>
       <c r="R49" t="n">
-        <v>6697350</v>
+        <v>6697386</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6275,26 +6295,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6311,7 +6311,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119810435</v>
+        <v>119810437</v>
       </c>
       <c r="B50" t="n">
         <v>78526</v>
@@ -6347,14 +6347,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>403786</v>
+        <v>403805</v>
       </c>
       <c r="R50" t="n">
-        <v>6697381</v>
+        <v>6697361</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6401,12 +6401,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6719,7 +6719,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119809124</v>
+        <v>119810847</v>
       </c>
       <c r="B54" t="n">
         <v>78526</v>
@@ -6759,10 +6759,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>403456</v>
+        <v>403886</v>
       </c>
       <c r="R54" t="n">
-        <v>6697335</v>
+        <v>6697427</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6821,7 +6821,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119810356</v>
+        <v>119809124</v>
       </c>
       <c r="B55" t="n">
         <v>78526</v>
@@ -6857,14 +6857,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>403789</v>
+        <v>403456</v>
       </c>
       <c r="R55" t="n">
-        <v>6697379</v>
+        <v>6697335</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6911,19 +6911,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119810328</v>
+        <v>119810356</v>
       </c>
       <c r="B56" t="n">
         <v>78526</v>
@@ -6963,10 +6963,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>403792</v>
+        <v>403789</v>
       </c>
       <c r="R56" t="n">
-        <v>6697361</v>
+        <v>6697379</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7025,7 +7025,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119810847</v>
+        <v>119810328</v>
       </c>
       <c r="B57" t="n">
         <v>78526</v>
@@ -7061,14 +7061,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>403886</v>
+        <v>403792</v>
       </c>
       <c r="R57" t="n">
-        <v>6697427</v>
+        <v>6697361</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7115,12 +7115,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -8677,7 +8677,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119810626</v>
+        <v>119808938</v>
       </c>
       <c r="B73" t="n">
         <v>78526</v>
@@ -8713,14 +8713,14 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Långmyren, Långmyren, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>403838</v>
+        <v>403325</v>
       </c>
       <c r="R73" t="n">
-        <v>6697353</v>
+        <v>6697298</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8779,7 +8779,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119808938</v>
+        <v>119810626</v>
       </c>
       <c r="B74" t="n">
         <v>78526</v>
@@ -8815,14 +8815,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>403325</v>
+        <v>403838</v>
       </c>
       <c r="R74" t="n">
-        <v>6697298</v>
+        <v>6697353</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -5985,10 +5985,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119810223</v>
+        <v>119810380</v>
       </c>
       <c r="B47" t="n">
-        <v>78645</v>
+        <v>78526</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5997,25 +5997,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1036</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Menegazzia terebrata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>403752</v>
+        <v>403769</v>
       </c>
       <c r="R47" t="n">
-        <v>6697350</v>
+        <v>6697386</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6071,26 +6071,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6107,7 +6087,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119810435</v>
+        <v>119810437</v>
       </c>
       <c r="B48" t="n">
         <v>78526</v>
@@ -6143,14 +6123,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>403786</v>
+        <v>403805</v>
       </c>
       <c r="R48" t="n">
-        <v>6697381</v>
+        <v>6697361</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6197,22 +6177,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119810380</v>
+        <v>119810223</v>
       </c>
       <c r="B49" t="n">
-        <v>78526</v>
+        <v>78645</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6221,25 +6201,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1036</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Menegazzia terebrata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6249,10 +6229,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>403769</v>
+        <v>403752</v>
       </c>
       <c r="R49" t="n">
-        <v>6697386</v>
+        <v>6697350</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6295,6 +6275,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6311,7 +6311,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119810437</v>
+        <v>119810435</v>
       </c>
       <c r="B50" t="n">
         <v>78526</v>
@@ -6347,14 +6347,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>403805</v>
+        <v>403786</v>
       </c>
       <c r="R50" t="n">
-        <v>6697361</v>
+        <v>6697381</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6401,12 +6401,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6515,10 +6515,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119810050</v>
+        <v>119809003</v>
       </c>
       <c r="B52" t="n">
-        <v>91832</v>
+        <v>78526</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6531,34 +6531,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>403566</v>
+        <v>403374</v>
       </c>
       <c r="R52" t="n">
-        <v>6697312</v>
+        <v>6697295</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6605,22 +6605,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119809003</v>
+        <v>119810050</v>
       </c>
       <c r="B53" t="n">
-        <v>78526</v>
+        <v>91832</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6633,34 +6633,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>403374</v>
+        <v>403566</v>
       </c>
       <c r="R53" t="n">
-        <v>6697295</v>
+        <v>6697312</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6707,12 +6707,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -7841,7 +7841,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119808919</v>
+        <v>119808923</v>
       </c>
       <c r="B65" t="n">
         <v>78526</v>
@@ -7877,14 +7877,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Långmyren, Långmyren, Vrm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>403384</v>
+        <v>403354</v>
       </c>
       <c r="R65" t="n">
-        <v>6697323</v>
+        <v>6697321</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7931,19 +7931,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119810145</v>
+        <v>119808919</v>
       </c>
       <c r="B66" t="n">
         <v>78526</v>
@@ -7983,10 +7983,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>403722</v>
+        <v>403384</v>
       </c>
       <c r="R66" t="n">
-        <v>6697347</v>
+        <v>6697323</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8045,7 +8045,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119808923</v>
+        <v>119810145</v>
       </c>
       <c r="B67" t="n">
         <v>78526</v>
@@ -8081,14 +8081,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>403354</v>
+        <v>403722</v>
       </c>
       <c r="R67" t="n">
-        <v>6697321</v>
+        <v>6697347</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8135,12 +8135,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8677,7 +8677,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119808938</v>
+        <v>119810626</v>
       </c>
       <c r="B73" t="n">
         <v>78526</v>
@@ -8713,14 +8713,14 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>403325</v>
+        <v>403838</v>
       </c>
       <c r="R73" t="n">
-        <v>6697298</v>
+        <v>6697353</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8779,7 +8779,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119810626</v>
+        <v>119808938</v>
       </c>
       <c r="B74" t="n">
         <v>78526</v>
@@ -8815,14 +8815,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Långmyren, Långmyren, Vrm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>403838</v>
+        <v>403325</v>
       </c>
       <c r="R74" t="n">
-        <v>6697353</v>
+        <v>6697298</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9187,7 +9187,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119810604</v>
+        <v>119808924</v>
       </c>
       <c r="B78" t="n">
         <v>78526</v>
@@ -9223,14 +9223,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>403860</v>
+        <v>403362</v>
       </c>
       <c r="R78" t="n">
-        <v>6697352</v>
+        <v>6697324</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9277,19 +9277,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119810895</v>
+        <v>119810604</v>
       </c>
       <c r="B79" t="n">
         <v>78526</v>
@@ -9325,14 +9325,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>403809</v>
+        <v>403860</v>
       </c>
       <c r="R79" t="n">
-        <v>6697436</v>
+        <v>6697352</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9379,19 +9379,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119808924</v>
+        <v>119810895</v>
       </c>
       <c r="B80" t="n">
         <v>78526</v>
@@ -9431,10 +9431,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>403362</v>
+        <v>403809</v>
       </c>
       <c r="R80" t="n">
-        <v>6697324</v>
+        <v>6697436</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -5985,10 +5985,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119810380</v>
+        <v>119810223</v>
       </c>
       <c r="B47" t="n">
-        <v>78526</v>
+        <v>78645</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5997,25 +5997,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1036</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Menegazzia terebrata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>403769</v>
+        <v>403752</v>
       </c>
       <c r="R47" t="n">
-        <v>6697386</v>
+        <v>6697350</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6071,6 +6071,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6087,7 +6107,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119810437</v>
+        <v>119810435</v>
       </c>
       <c r="B48" t="n">
         <v>78526</v>
@@ -6123,14 +6143,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>403805</v>
+        <v>403786</v>
       </c>
       <c r="R48" t="n">
-        <v>6697361</v>
+        <v>6697381</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6177,22 +6197,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119810223</v>
+        <v>119810380</v>
       </c>
       <c r="B49" t="n">
-        <v>78645</v>
+        <v>78526</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6201,25 +6221,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1036</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Menegazzia terebrata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6229,10 +6249,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>403752</v>
+        <v>403769</v>
       </c>
       <c r="R49" t="n">
-        <v>6697350</v>
+        <v>6697386</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6275,26 +6295,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6311,7 +6311,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119810435</v>
+        <v>119810437</v>
       </c>
       <c r="B50" t="n">
         <v>78526</v>
@@ -6347,14 +6347,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>403786</v>
+        <v>403805</v>
       </c>
       <c r="R50" t="n">
-        <v>6697381</v>
+        <v>6697361</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6401,12 +6401,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -7841,7 +7841,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119808923</v>
+        <v>119808919</v>
       </c>
       <c r="B65" t="n">
         <v>78526</v>
@@ -7877,14 +7877,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>403354</v>
+        <v>403384</v>
       </c>
       <c r="R65" t="n">
-        <v>6697321</v>
+        <v>6697323</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7931,19 +7931,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119808919</v>
+        <v>119810145</v>
       </c>
       <c r="B66" t="n">
         <v>78526</v>
@@ -7983,10 +7983,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>403384</v>
+        <v>403722</v>
       </c>
       <c r="R66" t="n">
-        <v>6697323</v>
+        <v>6697347</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8045,7 +8045,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119810145</v>
+        <v>119808923</v>
       </c>
       <c r="B67" t="n">
         <v>78526</v>
@@ -8081,14 +8081,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Långmyren, Långmyren, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>403722</v>
+        <v>403354</v>
       </c>
       <c r="R67" t="n">
-        <v>6697347</v>
+        <v>6697321</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8135,12 +8135,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8677,7 +8677,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119810626</v>
+        <v>119808938</v>
       </c>
       <c r="B73" t="n">
         <v>78526</v>
@@ -8713,14 +8713,14 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Långmyren, Långmyren, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>403838</v>
+        <v>403325</v>
       </c>
       <c r="R73" t="n">
-        <v>6697353</v>
+        <v>6697298</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8779,7 +8779,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119808938</v>
+        <v>119810626</v>
       </c>
       <c r="B74" t="n">
         <v>78526</v>
@@ -8815,14 +8815,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>403325</v>
+        <v>403838</v>
       </c>
       <c r="R74" t="n">
-        <v>6697298</v>
+        <v>6697353</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9187,7 +9187,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119808924</v>
+        <v>119810604</v>
       </c>
       <c r="B78" t="n">
         <v>78526</v>
@@ -9223,14 +9223,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>403362</v>
+        <v>403860</v>
       </c>
       <c r="R78" t="n">
-        <v>6697324</v>
+        <v>6697352</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9277,19 +9277,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119810604</v>
+        <v>119810895</v>
       </c>
       <c r="B79" t="n">
         <v>78526</v>
@@ -9325,14 +9325,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>403860</v>
+        <v>403809</v>
       </c>
       <c r="R79" t="n">
-        <v>6697352</v>
+        <v>6697436</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9379,19 +9379,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119810895</v>
+        <v>119808924</v>
       </c>
       <c r="B80" t="n">
         <v>78526</v>
@@ -9431,10 +9431,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>403809</v>
+        <v>403362</v>
       </c>
       <c r="R80" t="n">
-        <v>6697436</v>
+        <v>6697324</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -5985,10 +5985,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119810223</v>
+        <v>119810380</v>
       </c>
       <c r="B47" t="n">
-        <v>78645</v>
+        <v>78526</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5997,25 +5997,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1036</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Menegazzia terebrata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>403752</v>
+        <v>403769</v>
       </c>
       <c r="R47" t="n">
-        <v>6697350</v>
+        <v>6697386</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6071,26 +6071,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6107,7 +6087,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119810435</v>
+        <v>119810437</v>
       </c>
       <c r="B48" t="n">
         <v>78526</v>
@@ -6143,14 +6123,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>403786</v>
+        <v>403805</v>
       </c>
       <c r="R48" t="n">
-        <v>6697381</v>
+        <v>6697361</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6197,22 +6177,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119810380</v>
+        <v>119810223</v>
       </c>
       <c r="B49" t="n">
-        <v>78526</v>
+        <v>78645</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6221,25 +6201,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1036</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Menegazzia terebrata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6249,10 +6229,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>403769</v>
+        <v>403752</v>
       </c>
       <c r="R49" t="n">
-        <v>6697386</v>
+        <v>6697350</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6295,6 +6275,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6311,7 +6311,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119810437</v>
+        <v>119810435</v>
       </c>
       <c r="B50" t="n">
         <v>78526</v>
@@ -6347,14 +6347,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>403805</v>
+        <v>403786</v>
       </c>
       <c r="R50" t="n">
-        <v>6697361</v>
+        <v>6697381</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6401,12 +6401,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6515,10 +6515,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119809003</v>
+        <v>119810050</v>
       </c>
       <c r="B52" t="n">
-        <v>78526</v>
+        <v>91832</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6531,34 +6531,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>403374</v>
+        <v>403566</v>
       </c>
       <c r="R52" t="n">
-        <v>6697295</v>
+        <v>6697312</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6605,22 +6605,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119810050</v>
+        <v>119809003</v>
       </c>
       <c r="B53" t="n">
-        <v>91832</v>
+        <v>78526</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6633,34 +6633,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>403566</v>
+        <v>403374</v>
       </c>
       <c r="R53" t="n">
-        <v>6697312</v>
+        <v>6697295</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6707,12 +6707,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -5067,10 +5067,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119810892</v>
+        <v>119809838</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>79583</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5079,38 +5079,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>403853</v>
+        <v>403506</v>
       </c>
       <c r="R38" t="n">
-        <v>6697438</v>
+        <v>6697332</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5154,25 +5154,45 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Betula</t>
+        </is>
+      </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119808909</v>
+        <v>119808938</v>
       </c>
       <c r="B39" t="n">
-        <v>91852</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5181,38 +5201,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Långmyren, Långmyren, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>403397</v>
+        <v>403325</v>
       </c>
       <c r="R39" t="n">
-        <v>6697336</v>
+        <v>6697298</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5259,22 +5279,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119810877</v>
+        <v>119810437</v>
       </c>
       <c r="B40" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5311,10 +5331,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>403847</v>
+        <v>403805</v>
       </c>
       <c r="R40" t="n">
-        <v>6697449</v>
+        <v>6697361</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5373,10 +5393,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119810823</v>
+        <v>119809124</v>
       </c>
       <c r="B41" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5409,14 +5429,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>403887</v>
+        <v>403456</v>
       </c>
       <c r="R41" t="n">
-        <v>6697351</v>
+        <v>6697335</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5463,22 +5483,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119810057</v>
+        <v>119810877</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5511,14 +5531,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>403566</v>
+        <v>403847</v>
       </c>
       <c r="R42" t="n">
-        <v>6697312</v>
+        <v>6697449</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5565,12 +5585,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5580,7 +5600,7 @@
         <v>119810170</v>
       </c>
       <c r="B43" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5679,10 +5699,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119810334</v>
+        <v>119809202</v>
       </c>
       <c r="B44" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5715,14 +5735,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>403764</v>
+        <v>403485</v>
       </c>
       <c r="R44" t="n">
-        <v>6697370</v>
+        <v>6697329</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5769,22 +5789,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119810449</v>
+        <v>119810223</v>
       </c>
       <c r="B45" t="n">
-        <v>78526</v>
+        <v>78661</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5793,25 +5813,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1036</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Menegazzia terebrata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5821,10 +5841,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>403791</v>
+        <v>403752</v>
       </c>
       <c r="R45" t="n">
-        <v>6697346</v>
+        <v>6697350</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5867,6 +5887,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5883,10 +5923,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119810243</v>
+        <v>119810264</v>
       </c>
       <c r="B46" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5919,14 +5959,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Hallgruvkärret, Hallgruvkärret, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>403752</v>
+        <v>403777</v>
       </c>
       <c r="R46" t="n">
-        <v>6697350</v>
+        <v>6697344</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5973,22 +6013,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119810380</v>
+        <v>119808919</v>
       </c>
       <c r="B47" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6025,10 +6065,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>403769</v>
+        <v>403384</v>
       </c>
       <c r="R47" t="n">
-        <v>6697386</v>
+        <v>6697323</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6087,10 +6127,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119810437</v>
+        <v>119810380</v>
       </c>
       <c r="B48" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6127,10 +6167,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>403805</v>
+        <v>403769</v>
       </c>
       <c r="R48" t="n">
-        <v>6697361</v>
+        <v>6697386</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6189,10 +6229,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119810223</v>
+        <v>119810876</v>
       </c>
       <c r="B49" t="n">
-        <v>78645</v>
+        <v>78542</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6201,38 +6241,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1036</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Menegazzia terebrata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>403752</v>
+        <v>403852</v>
       </c>
       <c r="R49" t="n">
-        <v>6697350</v>
+        <v>6697437</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6276,45 +6316,25 @@
       <c r="AG49" t="b">
         <v>0</v>
       </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Alnus glutinosa</t>
-        </is>
-      </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119810435</v>
+        <v>119810895</v>
       </c>
       <c r="B50" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6347,14 +6367,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>403786</v>
+        <v>403809</v>
       </c>
       <c r="R50" t="n">
-        <v>6697381</v>
+        <v>6697436</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6401,22 +6421,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119810876</v>
+        <v>119809028</v>
       </c>
       <c r="B51" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6449,14 +6469,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>403852</v>
+        <v>403394</v>
       </c>
       <c r="R51" t="n">
-        <v>6697437</v>
+        <v>6697322</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6503,22 +6523,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119810050</v>
+        <v>119810421</v>
       </c>
       <c r="B52" t="n">
-        <v>91832</v>
+        <v>78542</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6531,34 +6551,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>403566</v>
+        <v>403786</v>
       </c>
       <c r="R52" t="n">
-        <v>6697312</v>
+        <v>6697381</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6617,10 +6637,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119809003</v>
+        <v>119810626</v>
       </c>
       <c r="B53" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6653,14 +6673,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>403374</v>
+        <v>403838</v>
       </c>
       <c r="R53" t="n">
-        <v>6697295</v>
+        <v>6697353</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6707,22 +6727,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119810847</v>
+        <v>119808924</v>
       </c>
       <c r="B54" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6759,10 +6779,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>403886</v>
+        <v>403362</v>
       </c>
       <c r="R54" t="n">
-        <v>6697427</v>
+        <v>6697324</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6821,10 +6841,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119809124</v>
+        <v>119810328</v>
       </c>
       <c r="B55" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6857,14 +6877,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>403456</v>
+        <v>403792</v>
       </c>
       <c r="R55" t="n">
-        <v>6697335</v>
+        <v>6697361</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6911,22 +6931,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119810356</v>
+        <v>119810847</v>
       </c>
       <c r="B56" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6959,14 +6979,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>403789</v>
+        <v>403886</v>
       </c>
       <c r="R56" t="n">
-        <v>6697379</v>
+        <v>6697427</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7013,22 +7033,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119810328</v>
+        <v>119808909</v>
       </c>
       <c r="B57" t="n">
-        <v>78526</v>
+        <v>91870</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7037,38 +7057,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>403792</v>
+        <v>403397</v>
       </c>
       <c r="R57" t="n">
-        <v>6697361</v>
+        <v>6697336</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7115,22 +7135,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119808930</v>
+        <v>119810057</v>
       </c>
       <c r="B58" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7163,14 +7183,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>403363</v>
+        <v>403566</v>
       </c>
       <c r="R58" t="n">
-        <v>6697334</v>
+        <v>6697312</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7217,22 +7237,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119809225</v>
+        <v>119810604</v>
       </c>
       <c r="B59" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7265,14 +7285,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>403479</v>
+        <v>403860</v>
       </c>
       <c r="R59" t="n">
-        <v>6697356</v>
+        <v>6697352</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7319,22 +7339,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119810088</v>
+        <v>119808923</v>
       </c>
       <c r="B60" t="n">
-        <v>91884</v>
+        <v>78542</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7347,34 +7367,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Långmyren, Långmyren, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>403566</v>
+        <v>403354</v>
       </c>
       <c r="R60" t="n">
-        <v>6697312</v>
+        <v>6697321</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7433,10 +7453,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119809028</v>
+        <v>119810823</v>
       </c>
       <c r="B61" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7469,14 +7489,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>403394</v>
+        <v>403887</v>
       </c>
       <c r="R61" t="n">
-        <v>6697322</v>
+        <v>6697351</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7523,22 +7543,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119809202</v>
+        <v>119810677</v>
       </c>
       <c r="B62" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7571,14 +7591,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>403485</v>
+        <v>403862</v>
       </c>
       <c r="R62" t="n">
-        <v>6697329</v>
+        <v>6697372</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7625,12 +7645,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7640,7 +7660,7 @@
         <v>119809326</v>
       </c>
       <c r="B63" t="n">
-        <v>57463</v>
+        <v>57473</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7739,10 +7759,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119809044</v>
+        <v>119810449</v>
       </c>
       <c r="B64" t="n">
-        <v>91852</v>
+        <v>78542</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7751,25 +7771,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7779,10 +7799,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>403399</v>
+        <v>403791</v>
       </c>
       <c r="R64" t="n">
-        <v>6697339</v>
+        <v>6697346</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7841,10 +7861,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119808919</v>
+        <v>119810892</v>
       </c>
       <c r="B65" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7877,14 +7897,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>403384</v>
+        <v>403853</v>
       </c>
       <c r="R65" t="n">
-        <v>6697323</v>
+        <v>6697438</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7931,22 +7951,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119810145</v>
+        <v>119810651</v>
       </c>
       <c r="B66" t="n">
-        <v>78526</v>
+        <v>74646</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7959,21 +7979,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7983,10 +8003,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>403722</v>
+        <v>403841</v>
       </c>
       <c r="R66" t="n">
-        <v>6697347</v>
+        <v>6697378</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8045,10 +8065,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119808923</v>
+        <v>119808930</v>
       </c>
       <c r="B67" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8081,14 +8101,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>403354</v>
+        <v>403363</v>
       </c>
       <c r="R67" t="n">
-        <v>6697321</v>
+        <v>6697334</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8135,22 +8155,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119810677</v>
+        <v>119810356</v>
       </c>
       <c r="B68" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8183,14 +8203,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>403862</v>
+        <v>403789</v>
       </c>
       <c r="R68" t="n">
-        <v>6697372</v>
+        <v>6697379</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8237,22 +8257,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119810651</v>
+        <v>119810243</v>
       </c>
       <c r="B69" t="n">
-        <v>74630</v>
+        <v>78542</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8265,21 +8285,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8289,10 +8309,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>403841</v>
+        <v>403752</v>
       </c>
       <c r="R69" t="n">
-        <v>6697378</v>
+        <v>6697350</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8351,10 +8371,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119810264</v>
+        <v>119810334</v>
       </c>
       <c r="B70" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8387,14 +8407,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Hallgruvkärret, Hallgruvkärret, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>403777</v>
+        <v>403764</v>
       </c>
       <c r="R70" t="n">
-        <v>6697344</v>
+        <v>6697370</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8441,22 +8461,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119810619</v>
+        <v>119810050</v>
       </c>
       <c r="B71" t="n">
-        <v>74577</v>
+        <v>91850</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8465,38 +8485,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6426</v>
+        <v>4361</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>403841</v>
+        <v>403566</v>
       </c>
       <c r="R71" t="n">
-        <v>6697378</v>
+        <v>6697312</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8543,22 +8563,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119809838</v>
+        <v>119810431</v>
       </c>
       <c r="B72" t="n">
-        <v>79567</v>
+        <v>78542</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8567,25 +8587,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8595,10 +8615,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>403506</v>
+        <v>403807</v>
       </c>
       <c r="R72" t="n">
-        <v>6697332</v>
+        <v>6697384</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8641,26 +8661,6 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Betula</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8677,10 +8677,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119808938</v>
+        <v>119810619</v>
       </c>
       <c r="B73" t="n">
-        <v>78526</v>
+        <v>74593</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8689,38 +8689,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>403325</v>
+        <v>403841</v>
       </c>
       <c r="R73" t="n">
-        <v>6697298</v>
+        <v>6697378</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8767,22 +8767,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119810626</v>
+        <v>119808937</v>
       </c>
       <c r="B74" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8815,14 +8815,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>403838</v>
+        <v>403330</v>
       </c>
       <c r="R74" t="n">
-        <v>6697353</v>
+        <v>6697322</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8869,12 +8869,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8884,7 +8884,7 @@
         <v>119810179</v>
       </c>
       <c r="B75" t="n">
-        <v>74577</v>
+        <v>74593</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8983,10 +8983,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119810431</v>
+        <v>119810088</v>
       </c>
       <c r="B76" t="n">
-        <v>78526</v>
+        <v>91902</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8999,34 +8999,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>403807</v>
+        <v>403566</v>
       </c>
       <c r="R76" t="n">
-        <v>6697384</v>
+        <v>6697312</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9073,22 +9073,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119808937</v>
+        <v>119810145</v>
       </c>
       <c r="B77" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9125,10 +9125,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>403330</v>
+        <v>403722</v>
       </c>
       <c r="R77" t="n">
-        <v>6697322</v>
+        <v>6697347</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9187,10 +9187,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119810604</v>
+        <v>119809003</v>
       </c>
       <c r="B78" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9223,14 +9223,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>403860</v>
+        <v>403374</v>
       </c>
       <c r="R78" t="n">
-        <v>6697352</v>
+        <v>6697295</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9277,22 +9277,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119810895</v>
+        <v>119809225</v>
       </c>
       <c r="B79" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9329,10 +9329,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>403809</v>
+        <v>403479</v>
       </c>
       <c r="R79" t="n">
-        <v>6697436</v>
+        <v>6697356</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9391,10 +9391,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119808924</v>
+        <v>119809044</v>
       </c>
       <c r="B80" t="n">
-        <v>78526</v>
+        <v>91870</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9403,25 +9403,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9431,10 +9431,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>403362</v>
+        <v>403399</v>
       </c>
       <c r="R80" t="n">
-        <v>6697324</v>
+        <v>6697339</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -5067,10 +5067,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119809838</v>
+        <v>119808938</v>
       </c>
       <c r="B38" t="n">
-        <v>79583</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5079,38 +5079,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Långmyren, Långmyren, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>403506</v>
+        <v>403325</v>
       </c>
       <c r="R38" t="n">
-        <v>6697332</v>
+        <v>6697298</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5154,42 +5154,22 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Betula</t>
-        </is>
-      </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119808938</v>
+        <v>119810437</v>
       </c>
       <c r="B39" t="n">
         <v>78542</v>
@@ -5225,14 +5205,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>403325</v>
+        <v>403805</v>
       </c>
       <c r="R39" t="n">
-        <v>6697298</v>
+        <v>6697361</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5279,22 +5259,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119810437</v>
+        <v>119809838</v>
       </c>
       <c r="B40" t="n">
-        <v>78542</v>
+        <v>79583</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5303,25 +5283,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5331,10 +5311,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>403805</v>
+        <v>403506</v>
       </c>
       <c r="R40" t="n">
-        <v>6697361</v>
+        <v>6697332</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5377,6 +5357,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -9289,10 +9289,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119809225</v>
+        <v>119809044</v>
       </c>
       <c r="B79" t="n">
-        <v>78542</v>
+        <v>91870</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9301,25 +9301,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9329,10 +9329,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>403479</v>
+        <v>403399</v>
       </c>
       <c r="R79" t="n">
-        <v>6697356</v>
+        <v>6697339</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9391,10 +9391,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119809044</v>
+        <v>119809225</v>
       </c>
       <c r="B80" t="n">
-        <v>91870</v>
+        <v>78542</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9403,25 +9403,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9431,10 +9431,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>403399</v>
+        <v>403479</v>
       </c>
       <c r="R80" t="n">
-        <v>6697339</v>
+        <v>6697356</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -5067,7 +5067,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119808938</v>
+        <v>119810057</v>
       </c>
       <c r="B38" t="n">
         <v>78542</v>
@@ -5103,14 +5103,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>403325</v>
+        <v>403566</v>
       </c>
       <c r="R38" t="n">
-        <v>6697298</v>
+        <v>6697312</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5169,7 +5169,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119810437</v>
+        <v>119810877</v>
       </c>
       <c r="B39" t="n">
         <v>78542</v>
@@ -5209,10 +5209,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>403805</v>
+        <v>403847</v>
       </c>
       <c r="R39" t="n">
-        <v>6697361</v>
+        <v>6697449</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5271,10 +5271,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119809838</v>
+        <v>119810604</v>
       </c>
       <c r="B40" t="n">
-        <v>79583</v>
+        <v>78542</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5283,38 +5283,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>403506</v>
+        <v>403860</v>
       </c>
       <c r="R40" t="n">
-        <v>6697332</v>
+        <v>6697352</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5358,42 +5358,22 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Betula</t>
-        </is>
-      </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119809124</v>
+        <v>119808919</v>
       </c>
       <c r="B41" t="n">
         <v>78542</v>
@@ -5433,10 +5413,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>403456</v>
+        <v>403384</v>
       </c>
       <c r="R41" t="n">
-        <v>6697335</v>
+        <v>6697323</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5495,7 +5475,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119810877</v>
+        <v>119810847</v>
       </c>
       <c r="B42" t="n">
         <v>78542</v>
@@ -5535,10 +5515,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>403847</v>
+        <v>403886</v>
       </c>
       <c r="R42" t="n">
-        <v>6697449</v>
+        <v>6697427</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5597,7 +5577,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119810170</v>
+        <v>119810677</v>
       </c>
       <c r="B43" t="n">
         <v>78542</v>
@@ -5633,14 +5613,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>403739</v>
+        <v>403862</v>
       </c>
       <c r="R43" t="n">
-        <v>6697375</v>
+        <v>6697372</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5687,19 +5667,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119809202</v>
+        <v>119810396</v>
       </c>
       <c r="B44" t="n">
         <v>78542</v>
@@ -5735,14 +5715,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>403485</v>
+        <v>403786</v>
       </c>
       <c r="R44" t="n">
-        <v>6697329</v>
+        <v>6697381</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5801,10 +5781,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119810223</v>
+        <v>119810876</v>
       </c>
       <c r="B45" t="n">
-        <v>78661</v>
+        <v>78542</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5813,38 +5793,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1036</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Menegazzia terebrata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>403752</v>
+        <v>403852</v>
       </c>
       <c r="R45" t="n">
-        <v>6697350</v>
+        <v>6697437</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5888,45 +5868,25 @@
       <c r="AG45" t="b">
         <v>0</v>
       </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Alnus glutinosa</t>
-        </is>
-      </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119810264</v>
+        <v>119810651</v>
       </c>
       <c r="B46" t="n">
-        <v>78542</v>
+        <v>74646</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5939,34 +5899,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hallgruvkärret, Hallgruvkärret, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>403777</v>
+        <v>403841</v>
       </c>
       <c r="R46" t="n">
-        <v>6697344</v>
+        <v>6697378</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6013,19 +5973,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119808919</v>
+        <v>119810145</v>
       </c>
       <c r="B47" t="n">
         <v>78542</v>
@@ -6065,10 +6025,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>403384</v>
+        <v>403722</v>
       </c>
       <c r="R47" t="n">
-        <v>6697323</v>
+        <v>6697347</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6127,7 +6087,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119810380</v>
+        <v>119808937</v>
       </c>
       <c r="B48" t="n">
         <v>78542</v>
@@ -6167,10 +6127,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>403769</v>
+        <v>403330</v>
       </c>
       <c r="R48" t="n">
-        <v>6697386</v>
+        <v>6697322</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6229,7 +6189,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119810876</v>
+        <v>119809028</v>
       </c>
       <c r="B49" t="n">
         <v>78542</v>
@@ -6265,14 +6225,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>403852</v>
+        <v>403394</v>
       </c>
       <c r="R49" t="n">
-        <v>6697437</v>
+        <v>6697322</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6319,19 +6279,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119810895</v>
+        <v>119810170</v>
       </c>
       <c r="B50" t="n">
         <v>78542</v>
@@ -6367,14 +6327,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>403809</v>
+        <v>403739</v>
       </c>
       <c r="R50" t="n">
-        <v>6697436</v>
+        <v>6697375</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6421,19 +6381,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119809028</v>
+        <v>119808924</v>
       </c>
       <c r="B51" t="n">
         <v>78542</v>
@@ -6473,10 +6433,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>403394</v>
+        <v>403362</v>
       </c>
       <c r="R51" t="n">
-        <v>6697322</v>
+        <v>6697324</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6535,7 +6495,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119810421</v>
+        <v>119810892</v>
       </c>
       <c r="B52" t="n">
         <v>78542</v>
@@ -6575,10 +6535,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>403786</v>
+        <v>403853</v>
       </c>
       <c r="R52" t="n">
-        <v>6697381</v>
+        <v>6697438</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6637,10 +6597,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119810626</v>
+        <v>119809326</v>
       </c>
       <c r="B53" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6653,34 +6613,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>403838</v>
+        <v>403487</v>
       </c>
       <c r="R53" t="n">
-        <v>6697353</v>
+        <v>6697326</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6739,7 +6699,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119808924</v>
+        <v>119810380</v>
       </c>
       <c r="B54" t="n">
         <v>78542</v>
@@ -6779,10 +6739,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>403362</v>
+        <v>403769</v>
       </c>
       <c r="R54" t="n">
-        <v>6697324</v>
+        <v>6697386</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6841,7 +6801,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119810328</v>
+        <v>119810437</v>
       </c>
       <c r="B55" t="n">
         <v>78542</v>
@@ -6877,11 +6837,11 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>403792</v>
+        <v>403805</v>
       </c>
       <c r="R55" t="n">
         <v>6697361</v>
@@ -6931,19 +6891,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119810847</v>
+        <v>119810334</v>
       </c>
       <c r="B56" t="n">
         <v>78542</v>
@@ -6983,10 +6943,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>403886</v>
+        <v>403764</v>
       </c>
       <c r="R56" t="n">
-        <v>6697427</v>
+        <v>6697370</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7045,10 +7005,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119808909</v>
+        <v>119810088</v>
       </c>
       <c r="B57" t="n">
-        <v>91870</v>
+        <v>91902</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7057,38 +7017,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>403397</v>
+        <v>403566</v>
       </c>
       <c r="R57" t="n">
-        <v>6697336</v>
+        <v>6697312</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7135,19 +7095,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119810057</v>
+        <v>119810626</v>
       </c>
       <c r="B58" t="n">
         <v>78542</v>
@@ -7183,14 +7143,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>403566</v>
+        <v>403838</v>
       </c>
       <c r="R58" t="n">
-        <v>6697312</v>
+        <v>6697353</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7249,7 +7209,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119810604</v>
+        <v>119808930</v>
       </c>
       <c r="B59" t="n">
         <v>78542</v>
@@ -7285,14 +7245,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>403860</v>
+        <v>403363</v>
       </c>
       <c r="R59" t="n">
-        <v>6697352</v>
+        <v>6697334</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7339,19 +7299,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119808923</v>
+        <v>119809225</v>
       </c>
       <c r="B60" t="n">
         <v>78542</v>
@@ -7387,14 +7347,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>403354</v>
+        <v>403479</v>
       </c>
       <c r="R60" t="n">
-        <v>6697321</v>
+        <v>6697356</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7441,22 +7401,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119810823</v>
+        <v>119809044</v>
       </c>
       <c r="B61" t="n">
-        <v>78542</v>
+        <v>91870</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7465,38 +7425,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>403887</v>
+        <v>403399</v>
       </c>
       <c r="R61" t="n">
-        <v>6697351</v>
+        <v>6697339</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7543,19 +7503,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119810677</v>
+        <v>119810449</v>
       </c>
       <c r="B62" t="n">
         <v>78542</v>
@@ -7595,10 +7555,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>403862</v>
+        <v>403791</v>
       </c>
       <c r="R62" t="n">
-        <v>6697372</v>
+        <v>6697346</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7657,10 +7617,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119809326</v>
+        <v>119810356</v>
       </c>
       <c r="B63" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7673,34 +7633,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>403487</v>
+        <v>403789</v>
       </c>
       <c r="R63" t="n">
-        <v>6697326</v>
+        <v>6697379</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7759,7 +7719,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119810449</v>
+        <v>119809202</v>
       </c>
       <c r="B64" t="n">
         <v>78542</v>
@@ -7795,14 +7755,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>403791</v>
+        <v>403485</v>
       </c>
       <c r="R64" t="n">
-        <v>6697346</v>
+        <v>6697329</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7849,19 +7809,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119810892</v>
+        <v>119810328</v>
       </c>
       <c r="B65" t="n">
         <v>78542</v>
@@ -7901,10 +7861,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>403853</v>
+        <v>403792</v>
       </c>
       <c r="R65" t="n">
-        <v>6697438</v>
+        <v>6697361</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7963,10 +7923,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119810651</v>
+        <v>119810223</v>
       </c>
       <c r="B66" t="n">
-        <v>74646</v>
+        <v>78661</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7975,25 +7935,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>308</v>
+        <v>1036</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Hållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Menegazzia terebrata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8003,10 +7963,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>403841</v>
+        <v>403752</v>
       </c>
       <c r="R66" t="n">
-        <v>6697378</v>
+        <v>6697350</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8049,6 +8009,26 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8065,10 +8045,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119808930</v>
+        <v>119809838</v>
       </c>
       <c r="B67" t="n">
-        <v>78542</v>
+        <v>79583</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8077,25 +8057,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8105,10 +8085,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>403363</v>
+        <v>403506</v>
       </c>
       <c r="R67" t="n">
-        <v>6697334</v>
+        <v>6697332</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8151,6 +8131,26 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8167,7 +8167,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119810356</v>
+        <v>119810264</v>
       </c>
       <c r="B68" t="n">
         <v>78542</v>
@@ -8203,14 +8203,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Hallgruvkärret, Hallgruvkärret, Vrm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>403789</v>
+        <v>403777</v>
       </c>
       <c r="R68" t="n">
-        <v>6697379</v>
+        <v>6697344</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8269,7 +8269,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119810243</v>
+        <v>119808923</v>
       </c>
       <c r="B69" t="n">
         <v>78542</v>
@@ -8305,14 +8305,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Långmyren, Långmyren, Vrm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>403752</v>
+        <v>403354</v>
       </c>
       <c r="R69" t="n">
-        <v>6697350</v>
+        <v>6697321</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8359,19 +8359,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119810334</v>
+        <v>119810832</v>
       </c>
       <c r="B70" t="n">
         <v>78542</v>
@@ -8407,14 +8407,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>403764</v>
+        <v>403887</v>
       </c>
       <c r="R70" t="n">
-        <v>6697370</v>
+        <v>6697351</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8461,12 +8461,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8575,10 +8575,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119810431</v>
+        <v>119810179</v>
       </c>
       <c r="B72" t="n">
-        <v>78542</v>
+        <v>74593</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8587,25 +8587,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8615,10 +8615,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>403807</v>
+        <v>403744</v>
       </c>
       <c r="R72" t="n">
-        <v>6697384</v>
+        <v>6697356</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8677,10 +8677,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119810619</v>
+        <v>119808909</v>
       </c>
       <c r="B73" t="n">
-        <v>74593</v>
+        <v>91870</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8693,21 +8693,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6426</v>
+        <v>4366</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8717,10 +8717,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>403841</v>
+        <v>403397</v>
       </c>
       <c r="R73" t="n">
-        <v>6697378</v>
+        <v>6697336</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8779,7 +8779,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119808937</v>
+        <v>119809124</v>
       </c>
       <c r="B74" t="n">
         <v>78542</v>
@@ -8819,10 +8819,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>403330</v>
+        <v>403456</v>
       </c>
       <c r="R74" t="n">
-        <v>6697322</v>
+        <v>6697335</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8881,7 +8881,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119810179</v>
+        <v>119810619</v>
       </c>
       <c r="B75" t="n">
         <v>74593</v>
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>403744</v>
+        <v>403841</v>
       </c>
       <c r="R75" t="n">
-        <v>6697356</v>
+        <v>6697378</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8983,10 +8983,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119810088</v>
+        <v>119810895</v>
       </c>
       <c r="B76" t="n">
-        <v>91902</v>
+        <v>78542</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8999,34 +8999,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>403566</v>
+        <v>403809</v>
       </c>
       <c r="R76" t="n">
-        <v>6697312</v>
+        <v>6697436</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9073,19 +9073,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119810145</v>
+        <v>119810431</v>
       </c>
       <c r="B77" t="n">
         <v>78542</v>
@@ -9125,10 +9125,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>403722</v>
+        <v>403807</v>
       </c>
       <c r="R77" t="n">
-        <v>6697347</v>
+        <v>6697384</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9187,7 +9187,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119809003</v>
+        <v>119810243</v>
       </c>
       <c r="B78" t="n">
         <v>78542</v>
@@ -9227,10 +9227,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>403374</v>
+        <v>403752</v>
       </c>
       <c r="R78" t="n">
-        <v>6697295</v>
+        <v>6697350</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9289,10 +9289,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119809044</v>
+        <v>119808938</v>
       </c>
       <c r="B79" t="n">
-        <v>91870</v>
+        <v>78542</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9301,38 +9301,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Långmyren, Långmyren, Vrm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>403399</v>
+        <v>403325</v>
       </c>
       <c r="R79" t="n">
-        <v>6697339</v>
+        <v>6697298</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9379,19 +9379,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119809225</v>
+        <v>119809003</v>
       </c>
       <c r="B80" t="n">
         <v>78542</v>
@@ -9431,10 +9431,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>403479</v>
+        <v>403374</v>
       </c>
       <c r="R80" t="n">
-        <v>6697356</v>
+        <v>6697295</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -5679,7 +5679,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119810396</v>
+        <v>119810145</v>
       </c>
       <c r="B44" t="n">
         <v>78542</v>
@@ -5715,14 +5715,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>403786</v>
+        <v>403722</v>
       </c>
       <c r="R44" t="n">
-        <v>6697381</v>
+        <v>6697347</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5769,19 +5769,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119810876</v>
+        <v>119810396</v>
       </c>
       <c r="B45" t="n">
         <v>78542</v>
@@ -5821,10 +5821,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>403852</v>
+        <v>403786</v>
       </c>
       <c r="R45" t="n">
-        <v>6697437</v>
+        <v>6697381</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5883,10 +5883,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119810651</v>
+        <v>119810876</v>
       </c>
       <c r="B46" t="n">
-        <v>74646</v>
+        <v>78542</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5899,34 +5899,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>403841</v>
+        <v>403852</v>
       </c>
       <c r="R46" t="n">
-        <v>6697378</v>
+        <v>6697437</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5973,19 +5973,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119810145</v>
+        <v>119808937</v>
       </c>
       <c r="B47" t="n">
         <v>78542</v>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>403722</v>
+        <v>403330</v>
       </c>
       <c r="R47" t="n">
-        <v>6697347</v>
+        <v>6697322</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6087,10 +6087,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119808937</v>
+        <v>119810651</v>
       </c>
       <c r="B48" t="n">
-        <v>78542</v>
+        <v>74646</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6103,21 +6103,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6127,10 +6127,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>403330</v>
+        <v>403841</v>
       </c>
       <c r="R48" t="n">
-        <v>6697322</v>
+        <v>6697378</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -5067,7 +5067,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119810057</v>
+        <v>119810145</v>
       </c>
       <c r="B38" t="n">
         <v>78542</v>
@@ -5103,14 +5103,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>403566</v>
+        <v>403722</v>
       </c>
       <c r="R38" t="n">
-        <v>6697312</v>
+        <v>6697347</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5157,22 +5157,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119810877</v>
+        <v>119810179</v>
       </c>
       <c r="B39" t="n">
-        <v>78542</v>
+        <v>74593</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5181,25 +5181,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5209,10 +5209,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>403847</v>
+        <v>403744</v>
       </c>
       <c r="R39" t="n">
-        <v>6697449</v>
+        <v>6697356</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5271,7 +5271,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119810604</v>
+        <v>119808938</v>
       </c>
       <c r="B40" t="n">
         <v>78542</v>
@@ -5307,14 +5307,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Långmyren, Långmyren, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>403860</v>
+        <v>403325</v>
       </c>
       <c r="R40" t="n">
-        <v>6697352</v>
+        <v>6697298</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5373,7 +5373,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119808919</v>
+        <v>119810457</v>
       </c>
       <c r="B41" t="n">
         <v>78542</v>
@@ -5409,14 +5409,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>403384</v>
+        <v>403786</v>
       </c>
       <c r="R41" t="n">
-        <v>6697323</v>
+        <v>6697381</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5463,12 +5463,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119810677</v>
+        <v>119810449</v>
       </c>
       <c r="B43" t="n">
         <v>78542</v>
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>403862</v>
+        <v>403791</v>
       </c>
       <c r="R43" t="n">
-        <v>6697372</v>
+        <v>6697346</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5679,10 +5679,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119810145</v>
+        <v>119810223</v>
       </c>
       <c r="B44" t="n">
-        <v>78542</v>
+        <v>78661</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5691,25 +5691,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1036</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Menegazzia terebrata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>403722</v>
+        <v>403752</v>
       </c>
       <c r="R44" t="n">
-        <v>6697347</v>
+        <v>6697350</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5765,6 +5765,26 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5781,7 +5801,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119810396</v>
+        <v>119810877</v>
       </c>
       <c r="B45" t="n">
         <v>78542</v>
@@ -5817,14 +5837,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>403786</v>
+        <v>403847</v>
       </c>
       <c r="R45" t="n">
-        <v>6697381</v>
+        <v>6697449</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5871,19 +5891,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119810876</v>
+        <v>119810334</v>
       </c>
       <c r="B46" t="n">
         <v>78542</v>
@@ -5919,14 +5939,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>403852</v>
+        <v>403764</v>
       </c>
       <c r="R46" t="n">
-        <v>6697437</v>
+        <v>6697370</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5973,19 +5993,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119808937</v>
+        <v>119808924</v>
       </c>
       <c r="B47" t="n">
         <v>78542</v>
@@ -6025,10 +6045,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>403330</v>
+        <v>403362</v>
       </c>
       <c r="R47" t="n">
-        <v>6697322</v>
+        <v>6697324</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6087,10 +6107,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119810651</v>
+        <v>119810604</v>
       </c>
       <c r="B48" t="n">
-        <v>74646</v>
+        <v>78542</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6103,34 +6123,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>403841</v>
+        <v>403860</v>
       </c>
       <c r="R48" t="n">
-        <v>6697378</v>
+        <v>6697352</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6177,22 +6197,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119809028</v>
+        <v>119809044</v>
       </c>
       <c r="B49" t="n">
-        <v>78542</v>
+        <v>91870</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6201,25 +6221,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6229,10 +6249,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>403394</v>
+        <v>403399</v>
       </c>
       <c r="R49" t="n">
-        <v>6697322</v>
+        <v>6697339</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6291,7 +6311,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119810170</v>
+        <v>119808919</v>
       </c>
       <c r="B50" t="n">
         <v>78542</v>
@@ -6327,14 +6347,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>403739</v>
+        <v>403384</v>
       </c>
       <c r="R50" t="n">
-        <v>6697375</v>
+        <v>6697323</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6381,19 +6401,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119808924</v>
+        <v>119810832</v>
       </c>
       <c r="B51" t="n">
         <v>78542</v>
@@ -6429,14 +6449,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>403362</v>
+        <v>403887</v>
       </c>
       <c r="R51" t="n">
-        <v>6697324</v>
+        <v>6697351</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6483,19 +6503,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119810892</v>
+        <v>119810328</v>
       </c>
       <c r="B52" t="n">
         <v>78542</v>
@@ -6535,10 +6555,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>403853</v>
+        <v>403792</v>
       </c>
       <c r="R52" t="n">
-        <v>6697438</v>
+        <v>6697361</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6597,10 +6617,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119809326</v>
+        <v>119808909</v>
       </c>
       <c r="B53" t="n">
-        <v>57473</v>
+        <v>91870</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6609,38 +6629,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>4366</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>403487</v>
+        <v>403397</v>
       </c>
       <c r="R53" t="n">
-        <v>6697326</v>
+        <v>6697336</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6687,19 +6707,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119810380</v>
+        <v>119809225</v>
       </c>
       <c r="B54" t="n">
         <v>78542</v>
@@ -6739,10 +6759,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>403769</v>
+        <v>403479</v>
       </c>
       <c r="R54" t="n">
-        <v>6697386</v>
+        <v>6697356</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6801,7 +6821,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119810437</v>
+        <v>119810170</v>
       </c>
       <c r="B55" t="n">
         <v>78542</v>
@@ -6837,14 +6857,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>403805</v>
+        <v>403739</v>
       </c>
       <c r="R55" t="n">
-        <v>6697361</v>
+        <v>6697375</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6891,19 +6911,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119810334</v>
+        <v>119810437</v>
       </c>
       <c r="B56" t="n">
         <v>78542</v>
@@ -6943,10 +6963,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>403764</v>
+        <v>403805</v>
       </c>
       <c r="R56" t="n">
-        <v>6697370</v>
+        <v>6697361</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7005,10 +7025,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119810088</v>
+        <v>119810626</v>
       </c>
       <c r="B57" t="n">
-        <v>91902</v>
+        <v>78542</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7021,34 +7041,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>403566</v>
+        <v>403838</v>
       </c>
       <c r="R57" t="n">
-        <v>6697312</v>
+        <v>6697353</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7107,7 +7127,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119810626</v>
+        <v>119810243</v>
       </c>
       <c r="B58" t="n">
         <v>78542</v>
@@ -7143,14 +7163,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>403838</v>
+        <v>403752</v>
       </c>
       <c r="R58" t="n">
-        <v>6697353</v>
+        <v>6697350</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7197,19 +7217,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119808930</v>
+        <v>119810876</v>
       </c>
       <c r="B59" t="n">
         <v>78542</v>
@@ -7245,14 +7265,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>403363</v>
+        <v>403852</v>
       </c>
       <c r="R59" t="n">
-        <v>6697334</v>
+        <v>6697437</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7299,19 +7319,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119809225</v>
+        <v>119808937</v>
       </c>
       <c r="B60" t="n">
         <v>78542</v>
@@ -7351,10 +7371,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>403479</v>
+        <v>403330</v>
       </c>
       <c r="R60" t="n">
-        <v>6697356</v>
+        <v>6697322</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7413,10 +7433,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119809044</v>
+        <v>119810057</v>
       </c>
       <c r="B61" t="n">
-        <v>91870</v>
+        <v>78542</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7425,38 +7445,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>403399</v>
+        <v>403566</v>
       </c>
       <c r="R61" t="n">
-        <v>6697339</v>
+        <v>6697312</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7503,19 +7523,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119810449</v>
+        <v>119808930</v>
       </c>
       <c r="B62" t="n">
         <v>78542</v>
@@ -7555,10 +7575,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>403791</v>
+        <v>403363</v>
       </c>
       <c r="R62" t="n">
-        <v>6697346</v>
+        <v>6697334</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7617,7 +7637,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119810356</v>
+        <v>119809028</v>
       </c>
       <c r="B63" t="n">
         <v>78542</v>
@@ -7653,14 +7673,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>403789</v>
+        <v>403394</v>
       </c>
       <c r="R63" t="n">
-        <v>6697379</v>
+        <v>6697322</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7707,22 +7727,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119809202</v>
+        <v>119810050</v>
       </c>
       <c r="B64" t="n">
-        <v>78542</v>
+        <v>91850</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7735,21 +7755,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7759,10 +7779,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>403485</v>
+        <v>403566</v>
       </c>
       <c r="R64" t="n">
-        <v>6697329</v>
+        <v>6697312</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7821,7 +7841,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119810328</v>
+        <v>119809124</v>
       </c>
       <c r="B65" t="n">
         <v>78542</v>
@@ -7857,14 +7877,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>403792</v>
+        <v>403456</v>
       </c>
       <c r="R65" t="n">
-        <v>6697361</v>
+        <v>6697335</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7911,22 +7931,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119810223</v>
+        <v>119810380</v>
       </c>
       <c r="B66" t="n">
-        <v>78661</v>
+        <v>78542</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7935,25 +7955,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1036</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Menegazzia terebrata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7963,10 +7983,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>403752</v>
+        <v>403769</v>
       </c>
       <c r="R66" t="n">
-        <v>6697350</v>
+        <v>6697386</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8009,26 +8029,6 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8045,10 +8045,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119809838</v>
+        <v>119808923</v>
       </c>
       <c r="B67" t="n">
-        <v>79583</v>
+        <v>78542</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8057,38 +8057,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Långmyren, Långmyren, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>403506</v>
+        <v>403354</v>
       </c>
       <c r="R67" t="n">
-        <v>6697332</v>
+        <v>6697321</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8132,42 +8132,22 @@
       <c r="AG67" t="b">
         <v>0</v>
       </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Betula</t>
-        </is>
-      </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119810264</v>
+        <v>119810892</v>
       </c>
       <c r="B68" t="n">
         <v>78542</v>
@@ -8203,14 +8183,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Hallgruvkärret, Hallgruvkärret, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>403777</v>
+        <v>403853</v>
       </c>
       <c r="R68" t="n">
-        <v>6697344</v>
+        <v>6697438</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8269,7 +8249,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119808923</v>
+        <v>119810356</v>
       </c>
       <c r="B69" t="n">
         <v>78542</v>
@@ -8305,14 +8285,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>403354</v>
+        <v>403789</v>
       </c>
       <c r="R69" t="n">
-        <v>6697321</v>
+        <v>6697379</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8371,10 +8351,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119810832</v>
+        <v>119810088</v>
       </c>
       <c r="B70" t="n">
-        <v>78542</v>
+        <v>91902</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8387,34 +8367,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>403887</v>
+        <v>403566</v>
       </c>
       <c r="R70" t="n">
-        <v>6697351</v>
+        <v>6697312</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8473,10 +8453,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119810050</v>
+        <v>119810895</v>
       </c>
       <c r="B71" t="n">
-        <v>91850</v>
+        <v>78542</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8489,34 +8469,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>403566</v>
+        <v>403809</v>
       </c>
       <c r="R71" t="n">
-        <v>6697312</v>
+        <v>6697436</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8563,22 +8543,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119810179</v>
+        <v>119809202</v>
       </c>
       <c r="B72" t="n">
-        <v>74593</v>
+        <v>78542</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8587,38 +8567,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>403744</v>
+        <v>403485</v>
       </c>
       <c r="R72" t="n">
-        <v>6697356</v>
+        <v>6697329</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8665,22 +8645,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119808909</v>
+        <v>119809326</v>
       </c>
       <c r="B73" t="n">
-        <v>91870</v>
+        <v>57473</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8689,38 +8669,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4366</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>403397</v>
+        <v>403487</v>
       </c>
       <c r="R73" t="n">
-        <v>6697336</v>
+        <v>6697326</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8767,22 +8747,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119809124</v>
+        <v>119809838</v>
       </c>
       <c r="B74" t="n">
-        <v>78542</v>
+        <v>79583</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8791,25 +8771,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8819,10 +8799,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>403456</v>
+        <v>403506</v>
       </c>
       <c r="R74" t="n">
-        <v>6697335</v>
+        <v>6697332</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8865,6 +8845,26 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8881,10 +8881,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119810619</v>
+        <v>119810651</v>
       </c>
       <c r="B75" t="n">
-        <v>74593</v>
+        <v>74646</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8893,25 +8893,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6426</v>
+        <v>308</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8983,10 +8983,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119810895</v>
+        <v>119810619</v>
       </c>
       <c r="B76" t="n">
-        <v>78542</v>
+        <v>74593</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8995,25 +8995,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9023,10 +9023,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>403809</v>
+        <v>403841</v>
       </c>
       <c r="R76" t="n">
-        <v>6697436</v>
+        <v>6697378</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9085,7 +9085,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119810431</v>
+        <v>119810677</v>
       </c>
       <c r="B77" t="n">
         <v>78542</v>
@@ -9125,10 +9125,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>403807</v>
+        <v>403862</v>
       </c>
       <c r="R77" t="n">
-        <v>6697384</v>
+        <v>6697372</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9187,7 +9187,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119810243</v>
+        <v>119810264</v>
       </c>
       <c r="B78" t="n">
         <v>78542</v>
@@ -9223,14 +9223,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Hallgruvkärret, Hallgruvkärret, Vrm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>403752</v>
+        <v>403777</v>
       </c>
       <c r="R78" t="n">
-        <v>6697350</v>
+        <v>6697344</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9277,19 +9277,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119808938</v>
+        <v>119809003</v>
       </c>
       <c r="B79" t="n">
         <v>78542</v>
@@ -9325,14 +9325,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>403325</v>
+        <v>403374</v>
       </c>
       <c r="R79" t="n">
-        <v>6697298</v>
+        <v>6697295</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9379,19 +9379,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119809003</v>
+        <v>119810431</v>
       </c>
       <c r="B80" t="n">
         <v>78542</v>
@@ -9431,10 +9431,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>403374</v>
+        <v>403807</v>
       </c>
       <c r="R80" t="n">
-        <v>6697295</v>
+        <v>6697384</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY80"/>
+  <dimension ref="A1:AY81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9491,6 +9491,113 @@
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>131379057</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79361</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1036</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Hållav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Menegazzia terebrata</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Stöen, Stöen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>403761</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6697361</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -9496,7 +9496,7 @@
         <v>131379057</v>
       </c>
       <c r="B81" t="n">
-        <v>79361</v>
+        <v>79363</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -9496,7 +9496,7 @@
         <v>131379057</v>
       </c>
       <c r="B81" t="n">
-        <v>79363</v>
+        <v>79364</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -9496,7 +9496,7 @@
         <v>131379057</v>
       </c>
       <c r="B81" t="n">
-        <v>79364</v>
+        <v>79365</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -9496,7 +9496,7 @@
         <v>131379057</v>
       </c>
       <c r="B81" t="n">
-        <v>79365</v>
+        <v>79368</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -9496,7 +9496,7 @@
         <v>131379057</v>
       </c>
       <c r="B81" t="n">
-        <v>79368</v>
+        <v>79369</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -9496,7 +9496,7 @@
         <v>131379057</v>
       </c>
       <c r="B81" t="n">
-        <v>79369</v>
+        <v>79375</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -9496,7 +9496,7 @@
         <v>131379057</v>
       </c>
       <c r="B81" t="n">
-        <v>79375</v>
+        <v>79376</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -9496,7 +9496,7 @@
         <v>131379057</v>
       </c>
       <c r="B81" t="n">
-        <v>79376</v>
+        <v>79379</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -9588,12 +9588,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -9496,7 +9496,7 @@
         <v>131379057</v>
       </c>
       <c r="B81" t="n">
-        <v>79379</v>
+        <v>79381</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY81"/>
+  <dimension ref="A1:AY83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7237489</v>
+        <v>7237490</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>403525.9503381445</v>
+        <v>403634</v>
       </c>
       <c r="R2" t="n">
-        <v>6697337.908375365</v>
+        <v>6697350</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -779,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>gammal gran</t>
+          <t>björkstubbe</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7237462</v>
+        <v>7237495</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>403618.2994679629</v>
+        <v>403751</v>
       </c>
       <c r="R3" t="n">
-        <v>6697290.958282025</v>
+        <v>6697338</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,21 +850,11 @@
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -901,7 +871,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>gammal gran</t>
+          <t>björkstubbe</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7237463</v>
+        <v>119810651</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björby, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403618.4437840724</v>
+        <v>403841</v>
       </c>
       <c r="R4" t="n">
-        <v>6697296.39294879</v>
+        <v>6697378</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,22 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2013-12-14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-12-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,16 +970,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>gammal gran</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1041,50 +986,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7237487</v>
+        <v>119810223</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1036</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Menegazzia terebrata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björby, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>403523.0336666075</v>
+        <v>403752</v>
       </c>
       <c r="R5" t="n">
-        <v>6697339.963518126</v>
+        <v>6697350</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,22 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2013-12-14</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2013-12-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,14 +1068,24 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>gammeltall</t>
+          <t>Bark on living woody plant # Alnus glutinosa</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1163,50 +1103,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7237459</v>
+        <v>131379057</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1036</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Menegazzia terebrata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>403629.6326988746</v>
+        <v>403761</v>
       </c>
       <c r="R6" t="n">
-        <v>6697307.467227004</v>
+        <v>6697361</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,22 +1168,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2013-12-14</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2013-12-14</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,41 +1194,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7237460</v>
+        <v>7237457</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1325,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>403621.7635813843</v>
+        <v>403623</v>
       </c>
       <c r="R7" t="n">
-        <v>6697290.866295104</v>
+        <v>6697326</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,21 +1278,11 @@
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1389,7 +1299,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>gammeltall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1410,12 +1320,7 @@
         <v>7237484</v>
       </c>
       <c r="B8" t="n">
-        <v>93276</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>403499.5821887026</v>
+        <v>403500</v>
       </c>
       <c r="R8" t="n">
-        <v>6697351.958234102</v>
+        <v>6697352</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,19 +1385,9 @@
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2013-12-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1529,50 +1424,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7237464</v>
+        <v>119810050</v>
       </c>
       <c r="B9" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>403618.4437840724</v>
+        <v>403566</v>
       </c>
       <c r="R9" t="n">
-        <v>6697296.39294879</v>
+        <v>6697312</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1599,22 +1489,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2013-12-14</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2013-12-14</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1625,76 +1505,61 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>gammal gran</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7237466</v>
+        <v>119808909</v>
       </c>
       <c r="B10" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björby, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403609.1892592426</v>
+        <v>403397</v>
       </c>
       <c r="R10" t="n">
-        <v>6697320.864656894</v>
+        <v>6697336</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1721,22 +1586,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2013-12-14</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2013-12-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1747,16 +1602,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>gammal gran</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1773,15 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7237495</v>
+        <v>119809044</v>
       </c>
       <c r="B11" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,34 +1629,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>308</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Björby, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403750.7773230559</v>
+        <v>403399</v>
       </c>
       <c r="R11" t="n">
-        <v>6697337.872131572</v>
+        <v>6697339</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1843,22 +1683,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2013-12-14</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2013-12-14</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1869,16 +1699,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>björkstubbe</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1895,15 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>7237480</v>
+        <v>119808917</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,34 +1726,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Björby, Vrm</t>
+          <t>Långmyren, Långmyren, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403473.7966443076</v>
+        <v>403399</v>
       </c>
       <c r="R12" t="n">
-        <v>6697350.666302864</v>
+        <v>6697345</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1965,22 +1780,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2013-12-14</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2013-12-14</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1991,45 +1796,30 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7237476</v>
+        <v>7237458</v>
       </c>
       <c r="B13" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2057,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403499.1446755055</v>
+        <v>403625</v>
       </c>
       <c r="R13" t="n">
-        <v>6697260.998745452</v>
+        <v>6697326</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2090,19 +1880,9 @@
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2013-12-14</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2139,37 +1919,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>7237482</v>
+        <v>7237459</v>
       </c>
       <c r="B14" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2179,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403483.5888475179</v>
+        <v>403630</v>
       </c>
       <c r="R14" t="n">
-        <v>6697346.450669656</v>
+        <v>6697307</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2212,21 +1987,11 @@
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2243,7 +2008,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>gammal gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2261,19 +2026,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>7237498</v>
+        <v>7237460</v>
       </c>
       <c r="B15" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2301,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403808.6690528746</v>
+        <v>403622</v>
       </c>
       <c r="R15" t="n">
-        <v>6697373.417314821</v>
+        <v>6697291</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2334,21 +2094,11 @@
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2365,7 +2115,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>äldre tall</t>
+          <t>gammeltall</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2383,37 +2133,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>7237457</v>
+        <v>7237462</v>
       </c>
       <c r="B16" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2423,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403622.7081593153</v>
+        <v>403618</v>
       </c>
       <c r="R16" t="n">
-        <v>6697326.438512738</v>
+        <v>6697291</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2456,21 +2201,11 @@
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2487,7 +2222,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gammal gran</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2505,37 +2240,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>7237468</v>
+        <v>7237463</v>
       </c>
       <c r="B17" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2545,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403600.4877958356</v>
+        <v>403618</v>
       </c>
       <c r="R17" t="n">
-        <v>6697310.218820809</v>
+        <v>6697296</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2578,19 +2308,9 @@
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2013-12-14</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2627,19 +2347,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>7237473</v>
+        <v>7237470</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2667,10 +2382,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403583.6058395304</v>
+        <v>403596</v>
       </c>
       <c r="R18" t="n">
-        <v>6697289.902088999</v>
+        <v>6697299</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2700,21 +2415,11 @@
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2731,7 +2436,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>gammeltall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2749,37 +2454,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>7237456</v>
+        <v>7237473</v>
       </c>
       <c r="B19" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2789,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403622.7081593153</v>
+        <v>403584</v>
       </c>
       <c r="R19" t="n">
-        <v>6697326.438512738</v>
+        <v>6697290</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2822,21 +2522,11 @@
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2853,7 +2543,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gammeltall</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2871,37 +2561,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>7237490</v>
+        <v>7237474</v>
       </c>
       <c r="B20" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2911,10 +2596,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403633.7300452855</v>
+        <v>403577</v>
       </c>
       <c r="R20" t="n">
-        <v>6697349.877193516</v>
+        <v>6697281</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2944,21 +2629,11 @@
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2975,7 +2650,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>björkstubbe</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2993,37 +2668,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>7237455</v>
+        <v>7237475</v>
       </c>
       <c r="B21" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3033,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403622.7081593153</v>
+        <v>403567</v>
       </c>
       <c r="R21" t="n">
-        <v>6697326.438512738</v>
+        <v>6697283</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3066,21 +2736,11 @@
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3097,7 +2757,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3115,19 +2775,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>7237474</v>
+        <v>7237476</v>
       </c>
       <c r="B22" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3155,10 +2810,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>403577.4311038099</v>
+        <v>403499</v>
       </c>
       <c r="R22" t="n">
-        <v>6697281.166733703</v>
+        <v>6697261</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3188,21 +2843,11 @@
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3219,7 +2864,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>gammeltall</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3237,19 +2882,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>7237493</v>
+        <v>7237477</v>
       </c>
       <c r="B23" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3277,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>403743.0529592836</v>
+        <v>403474</v>
       </c>
       <c r="R23" t="n">
-        <v>6697326.705717381</v>
+        <v>6697263</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3310,21 +2950,11 @@
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3341,7 +2971,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>äldre tall</t>
+          <t>gammeltall</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3359,37 +2989,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>7237483</v>
+        <v>7237478</v>
       </c>
       <c r="B24" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3399,10 +3024,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>403507.7453363559</v>
+        <v>403464</v>
       </c>
       <c r="R24" t="n">
-        <v>6697342.34755009</v>
+        <v>6697334</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3432,21 +3057,11 @@
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3463,7 +3078,7 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>gammal gran</t>
+          <t>gammeltall</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3481,37 +3096,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>7237461</v>
+        <v>7237480</v>
       </c>
       <c r="B25" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3521,10 +3131,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>403618.2994679629</v>
+        <v>403474</v>
       </c>
       <c r="R25" t="n">
-        <v>6697290.958282025</v>
+        <v>6697351</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3554,21 +3164,11 @@
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3585,7 +3185,7 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>gammal gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3603,19 +3203,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>7237458</v>
+        <v>7237485</v>
       </c>
       <c r="B26" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3643,10 +3238,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>403624.6876333193</v>
+        <v>403509</v>
       </c>
       <c r="R26" t="n">
-        <v>6697326.385950617</v>
+        <v>6697352</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3676,19 +3271,9 @@
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2013-12-14</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3725,37 +3310,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>7237481</v>
+        <v>7237487</v>
       </c>
       <c r="B27" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3765,10 +3345,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>403477.260701922</v>
+        <v>403523</v>
       </c>
       <c r="R27" t="n">
-        <v>6697350.574177527</v>
+        <v>6697340</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3798,21 +3378,11 @@
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3829,7 +3399,7 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>gammal gran</t>
+          <t>gammeltall</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3847,19 +3417,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>7237470</v>
+        <v>7237489</v>
       </c>
       <c r="B28" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3887,10 +3452,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>403596.227008959</v>
+        <v>403526</v>
       </c>
       <c r="R28" t="n">
-        <v>6697298.960611877</v>
+        <v>6697338</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3920,21 +3485,11 @@
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3951,7 +3506,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>gammal gran</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3969,19 +3524,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>7237485</v>
+        <v>7237491</v>
       </c>
       <c r="B29" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -4009,10 +3559,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>403508.9846270152</v>
+        <v>403686</v>
       </c>
       <c r="R29" t="n">
-        <v>6697351.708254084</v>
+        <v>6697330</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4042,21 +3592,11 @@
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4073,7 +3613,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>gammeltall</t>
+          <t>äldre tall</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4091,37 +3631,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>7237497</v>
+        <v>7237492</v>
       </c>
       <c r="B30" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4131,10 +3666,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>403759.4782699886</v>
+        <v>403723</v>
       </c>
       <c r="R30" t="n">
-        <v>6697348.518229119</v>
+        <v>6697318</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4164,21 +3699,11 @@
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4195,7 +3720,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>äldre tall</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4213,37 +3738,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>7237486</v>
+        <v>7237493</v>
       </c>
       <c r="B31" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4253,10 +3773,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>403509.2299357527</v>
+        <v>403743</v>
       </c>
       <c r="R31" t="n">
-        <v>6697342.308081314</v>
+        <v>6697327</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4286,21 +3806,11 @@
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4317,7 +3827,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>gammal björk</t>
+          <t>äldre tall</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4335,19 +3845,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>7237477</v>
+        <v>7237498</v>
       </c>
       <c r="B32" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4375,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>403474.4402163293</v>
+        <v>403809</v>
       </c>
       <c r="R32" t="n">
-        <v>6697263.138896762</v>
+        <v>6697373</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4408,21 +3913,11 @@
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2013-12-14</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4439,7 +3934,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>gammeltall</t>
+          <t>äldre tall</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4457,50 +3952,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>7237465</v>
+        <v>119808918</v>
       </c>
       <c r="B33" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Björby, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>403612.4171757771</v>
+        <v>403393</v>
       </c>
       <c r="R33" t="n">
-        <v>6697311.879625164</v>
+        <v>6697348</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4527,22 +4017,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2013-12-14</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2013-12-14</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4553,16 +4033,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>gammal gran</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4579,19 +4049,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>7237475</v>
+        <v>119808919</v>
       </c>
       <c r="B34" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4615,14 +4080,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Björby, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>403566.583240219</v>
+        <v>403384</v>
       </c>
       <c r="R34" t="n">
-        <v>6697282.938166026</v>
+        <v>6697323</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4649,22 +4114,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2013-12-14</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2013-12-14</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4675,16 +4130,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4701,19 +4146,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>7237492</v>
+        <v>119808923</v>
       </c>
       <c r="B35" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4737,14 +4177,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Björby, Vrm</t>
+          <t>Långmyren, Långmyren, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>403723.0092244347</v>
+        <v>403354</v>
       </c>
       <c r="R35" t="n">
-        <v>6697317.84366663</v>
+        <v>6697321</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4771,22 +4211,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2013-12-14</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2013-12-14</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4797,45 +4227,30 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>äldre tall</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>7237491</v>
+        <v>119808924</v>
       </c>
       <c r="B36" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4859,14 +4274,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Björby, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>403686.1955521599</v>
+        <v>403362</v>
       </c>
       <c r="R36" t="n">
-        <v>6697330.191675956</v>
+        <v>6697324</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4893,22 +4308,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2013-12-14</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2013-12-14</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4919,16 +4324,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>äldre tall</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4945,19 +4340,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>7237478</v>
+        <v>119808930</v>
       </c>
       <c r="B37" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4981,14 +4371,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Björby, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>403463.9474188598</v>
+        <v>403363</v>
       </c>
       <c r="R37" t="n">
-        <v>6697334.118532376</v>
+        <v>6697334</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5015,22 +4405,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2013-12-14</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2013-12-14</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5041,16 +4421,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>gammeltall</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5067,19 +4437,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119810145</v>
+        <v>119808937</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -5107,10 +4472,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>403722</v>
+        <v>403330</v>
       </c>
       <c r="R38" t="n">
-        <v>6697347</v>
+        <v>6697322</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5169,50 +4534,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119810179</v>
+        <v>119808938</v>
       </c>
       <c r="B39" t="n">
-        <v>74593</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Långmyren, Långmyren, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>403744</v>
+        <v>403325</v>
       </c>
       <c r="R39" t="n">
-        <v>6697356</v>
+        <v>6697298</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5259,31 +4619,26 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119808938</v>
+        <v>119809003</v>
       </c>
       <c r="B40" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -5307,14 +4662,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>403325</v>
+        <v>403374</v>
       </c>
       <c r="R40" t="n">
-        <v>6697298</v>
+        <v>6697295</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5361,31 +4716,26 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119810457</v>
+        <v>119809028</v>
       </c>
       <c r="B41" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -5409,14 +4759,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>403786</v>
+        <v>403394</v>
       </c>
       <c r="R41" t="n">
-        <v>6697381</v>
+        <v>6697322</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5463,31 +4813,26 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119810847</v>
+        <v>119809124</v>
       </c>
       <c r="B42" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5515,10 +4860,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>403886</v>
+        <v>403456</v>
       </c>
       <c r="R42" t="n">
-        <v>6697427</v>
+        <v>6697335</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5577,19 +4922,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119810449</v>
+        <v>119809202</v>
       </c>
       <c r="B43" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -5613,14 +4953,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>403791</v>
+        <v>403485</v>
       </c>
       <c r="R43" t="n">
-        <v>6697346</v>
+        <v>6697329</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5667,27 +5007,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119810223</v>
+        <v>119809225</v>
       </c>
       <c r="B44" t="n">
-        <v>78661</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5695,21 +5030,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1036</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Menegazzia terebrata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5719,10 +5054,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>403752</v>
+        <v>403479</v>
       </c>
       <c r="R44" t="n">
-        <v>6697350</v>
+        <v>6697356</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5765,26 +5100,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5801,19 +5116,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119810877</v>
+        <v>119810057</v>
       </c>
       <c r="B45" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5837,14 +5147,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>403847</v>
+        <v>403566</v>
       </c>
       <c r="R45" t="n">
-        <v>6697449</v>
+        <v>6697312</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5891,31 +5201,26 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119810334</v>
+        <v>119810145</v>
       </c>
       <c r="B46" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5943,10 +5248,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>403764</v>
+        <v>403722</v>
       </c>
       <c r="R46" t="n">
-        <v>6697370</v>
+        <v>6697347</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6005,19 +5310,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119808924</v>
+        <v>119810170</v>
       </c>
       <c r="B47" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -6041,14 +5341,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>403362</v>
+        <v>403739</v>
       </c>
       <c r="R47" t="n">
-        <v>6697324</v>
+        <v>6697375</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6095,31 +5395,26 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119810604</v>
+        <v>119810243</v>
       </c>
       <c r="B48" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -6143,14 +5438,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>403860</v>
+        <v>403752</v>
       </c>
       <c r="R48" t="n">
-        <v>6697352</v>
+        <v>6697350</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6197,62 +5492,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119809044</v>
+        <v>119810264</v>
       </c>
       <c r="B49" t="n">
-        <v>91870</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Hallgruvkärret, Hallgruvkärret, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>403399</v>
+        <v>403777</v>
       </c>
       <c r="R49" t="n">
-        <v>6697339</v>
+        <v>6697344</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6299,31 +5589,26 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119808919</v>
+        <v>119810328</v>
       </c>
       <c r="B50" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -6347,14 +5632,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>403384</v>
+        <v>403792</v>
       </c>
       <c r="R50" t="n">
-        <v>6697323</v>
+        <v>6697361</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6401,31 +5686,26 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119810832</v>
+        <v>119810334</v>
       </c>
       <c r="B51" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -6449,14 +5729,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>403887</v>
+        <v>403764</v>
       </c>
       <c r="R51" t="n">
-        <v>6697351</v>
+        <v>6697370</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6503,31 +5783,26 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119810328</v>
+        <v>119810356</v>
       </c>
       <c r="B52" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -6555,10 +5830,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>403792</v>
+        <v>403789</v>
       </c>
       <c r="R52" t="n">
-        <v>6697361</v>
+        <v>6697379</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6617,50 +5892,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119808909</v>
+        <v>119810375</v>
       </c>
       <c r="B53" t="n">
-        <v>91870</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>403397</v>
+        <v>403786</v>
       </c>
       <c r="R53" t="n">
-        <v>6697336</v>
+        <v>6697381</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6707,31 +5977,26 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119809225</v>
+        <v>119810380</v>
       </c>
       <c r="B54" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -6759,10 +6024,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>403479</v>
+        <v>403769</v>
       </c>
       <c r="R54" t="n">
-        <v>6697356</v>
+        <v>6697386</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6821,19 +6086,14 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119810170</v>
+        <v>119810431</v>
       </c>
       <c r="B55" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -6857,14 +6117,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>403739</v>
+        <v>403807</v>
       </c>
       <c r="R55" t="n">
-        <v>6697375</v>
+        <v>6697384</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6911,12 +6171,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6926,16 +6186,11 @@
         <v>119810437</v>
       </c>
       <c r="B56" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -7025,19 +6280,14 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119810626</v>
+        <v>119810449</v>
       </c>
       <c r="B57" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -7061,14 +6311,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>403838</v>
+        <v>403791</v>
       </c>
       <c r="R57" t="n">
-        <v>6697353</v>
+        <v>6697346</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7115,31 +6365,26 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119810243</v>
+        <v>119810604</v>
       </c>
       <c r="B58" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -7163,14 +6408,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>403752</v>
+        <v>403860</v>
       </c>
       <c r="R58" t="n">
-        <v>6697350</v>
+        <v>6697352</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7217,31 +6462,26 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119810876</v>
+        <v>119810626</v>
       </c>
       <c r="B59" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -7269,10 +6509,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>403852</v>
+        <v>403838</v>
       </c>
       <c r="R59" t="n">
-        <v>6697437</v>
+        <v>6697353</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7331,19 +6571,14 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119808937</v>
+        <v>119810677</v>
       </c>
       <c r="B60" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -7371,10 +6606,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>403330</v>
+        <v>403862</v>
       </c>
       <c r="R60" t="n">
-        <v>6697322</v>
+        <v>6697372</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7433,19 +6668,14 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119810057</v>
+        <v>119810823</v>
       </c>
       <c r="B61" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -7469,14 +6699,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>403566</v>
+        <v>403887</v>
       </c>
       <c r="R61" t="n">
-        <v>6697312</v>
+        <v>6697351</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7535,19 +6765,14 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119808930</v>
+        <v>119810830</v>
       </c>
       <c r="B62" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -7575,10 +6800,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>403363</v>
+        <v>403905</v>
       </c>
       <c r="R62" t="n">
-        <v>6697334</v>
+        <v>6697419</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7637,19 +6862,14 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119809028</v>
+        <v>119810847</v>
       </c>
       <c r="B63" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -7677,10 +6897,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>403394</v>
+        <v>403886</v>
       </c>
       <c r="R63" t="n">
-        <v>6697322</v>
+        <v>6697427</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7739,50 +6959,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119810050</v>
+        <v>119810876</v>
       </c>
       <c r="B64" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>403566</v>
+        <v>403852</v>
       </c>
       <c r="R64" t="n">
-        <v>6697312</v>
+        <v>6697437</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7841,19 +7056,14 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119809124</v>
+        <v>119810877</v>
       </c>
       <c r="B65" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -7881,10 +7091,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>403456</v>
+        <v>403847</v>
       </c>
       <c r="R65" t="n">
-        <v>6697335</v>
+        <v>6697449</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7943,19 +7153,14 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119810380</v>
+        <v>119810892</v>
       </c>
       <c r="B66" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -7979,14 +7184,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Holmberg, Holmberg, Vrm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>403769</v>
+        <v>403853</v>
       </c>
       <c r="R66" t="n">
-        <v>6697386</v>
+        <v>6697438</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8033,31 +7238,26 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119808923</v>
+        <v>119810895</v>
       </c>
       <c r="B67" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -8081,14 +7281,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Vrm</t>
+          <t>Björby, Björby, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>403354</v>
+        <v>403809</v>
       </c>
       <c r="R67" t="n">
-        <v>6697321</v>
+        <v>6697436</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8135,27 +7335,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119810892</v>
+        <v>7237461</v>
       </c>
       <c r="B68" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8163,34 +7358,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Vrm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>403853</v>
+        <v>403618</v>
       </c>
       <c r="R68" t="n">
-        <v>6697438</v>
+        <v>6697291</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8217,12 +7412,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2013-12-14</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2013-12-14</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8233,31 +7428,36 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119810356</v>
+        <v>7237464</v>
       </c>
       <c r="B69" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8265,34 +7465,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Holmberg, Holmberg, Vrm</t>
+          <t>Björby, Vrm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>403789</v>
+        <v>403618</v>
       </c>
       <c r="R69" t="n">
-        <v>6697379</v>
+        <v>6697296</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8319,12 +7519,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2013-12-14</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2013-12-14</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8335,31 +7535,36 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119810088</v>
+        <v>7237465</v>
       </c>
       <c r="B70" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8367,31 +7572,31 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5449</v>
+        <v>6426</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Vrm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>403566</v>
+        <v>403612</v>
       </c>
       <c r="R70" t="n">
         <v>6697312</v>
@@ -8421,12 +7626,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2013-12-14</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2013-12-14</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8437,31 +7642,36 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119810895</v>
+        <v>7237466</v>
       </c>
       <c r="B71" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8469,34 +7679,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Björby, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>403809</v>
+        <v>403609</v>
       </c>
       <c r="R71" t="n">
-        <v>6697436</v>
+        <v>6697321</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8523,12 +7733,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2013-12-14</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2013-12-14</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8539,6 +7749,16 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8555,15 +7775,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119809202</v>
+        <v>7237468</v>
       </c>
       <c r="B72" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8571,34 +7786,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>403485</v>
+        <v>403600</v>
       </c>
       <c r="R72" t="n">
-        <v>6697329</v>
+        <v>6697310</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8625,12 +7840,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2013-12-14</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2013-12-14</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8641,31 +7856,36 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119809326</v>
+        <v>7237481</v>
       </c>
       <c r="B73" t="n">
-        <v>57473</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8673,34 +7893,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>6426</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>403487</v>
+        <v>403477</v>
       </c>
       <c r="R73" t="n">
-        <v>6697326</v>
+        <v>6697351</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8727,12 +7947,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2013-12-14</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2013-12-14</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8743,66 +7963,71 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119809838</v>
+        <v>7237482</v>
       </c>
       <c r="B74" t="n">
-        <v>79583</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Björby, Vrm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>403506</v>
+        <v>403484</v>
       </c>
       <c r="R74" t="n">
-        <v>6697332</v>
+        <v>6697346</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8829,12 +8054,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2013-12-14</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2013-12-14</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8846,24 +8071,14 @@
       <c r="AG74" t="b">
         <v>0</v>
       </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>gammal gran</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8881,15 +8096,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119810651</v>
+        <v>7237483</v>
       </c>
       <c r="B75" t="n">
-        <v>74646</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8897,34 +8107,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>308</v>
+        <v>6426</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Björby, Vrm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>403841</v>
+        <v>403508</v>
       </c>
       <c r="R75" t="n">
-        <v>6697378</v>
+        <v>6697342</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8951,12 +8161,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2013-12-14</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2013-12-14</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8967,6 +8177,16 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -8983,19 +8203,14 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119810619</v>
+        <v>119810179</v>
       </c>
       <c r="B76" t="n">
-        <v>74593</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -9023,10 +8238,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>403841</v>
+        <v>403744</v>
       </c>
       <c r="R76" t="n">
-        <v>6697378</v>
+        <v>6697356</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9085,15 +8300,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119810677</v>
+        <v>119810619</v>
       </c>
       <c r="B77" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9101,21 +8311,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9125,10 +8335,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>403862</v>
+        <v>403841</v>
       </c>
       <c r="R77" t="n">
-        <v>6697372</v>
+        <v>6697378</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9187,15 +8397,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119810264</v>
+        <v>7237455</v>
       </c>
       <c r="B78" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9203,34 +8408,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Hallgruvkärret, Hallgruvkärret, Vrm</t>
+          <t>Björby, Vrm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>403777</v>
+        <v>403623</v>
       </c>
       <c r="R78" t="n">
-        <v>6697344</v>
+        <v>6697326</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9257,12 +8462,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2013-12-14</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2013-12-14</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9273,66 +8478,71 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119809003</v>
+        <v>7237497</v>
       </c>
       <c r="B79" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Björby, Vrm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>403374</v>
+        <v>403759</v>
       </c>
       <c r="R79" t="n">
-        <v>6697295</v>
+        <v>6697349</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9359,12 +8569,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2013-12-14</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2013-12-14</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9375,6 +8585,16 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9391,15 +8611,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119810431</v>
+        <v>119809326</v>
       </c>
       <c r="B80" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9407,34 +8622,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Björby, Björby, Vrm</t>
+          <t>Stöen, Stöen, Vrm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>403807</v>
+        <v>403487</v>
       </c>
       <c r="R80" t="n">
-        <v>6697384</v>
+        <v>6697326</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9481,57 +8696,57 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131379057</v>
+        <v>7237456</v>
       </c>
       <c r="B81" t="n">
-        <v>79381</v>
+        <v>80392</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1036</v>
+        <v>229497</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Hållav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Menegazzia terebrata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stöen, Stöen, Vrm</t>
+          <t>Björby, Vrm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>403761</v>
+        <v>403623</v>
       </c>
       <c r="R81" t="n">
-        <v>6697361</v>
+        <v>6697326</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9558,22 +8773,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>15:53</t>
+          <t>2013-12-14</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>15:53</t>
+          <t>2013-12-14</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9584,19 +8789,253 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>7237486</v>
+      </c>
+      <c r="B82" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Björby, Vrm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>403509</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6697342</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2013-12-14</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2013-12-14</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>gammal björk</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>119809838</v>
+      </c>
+      <c r="B83" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Björby, Björby, Vrm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>403506</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6697332</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Betula</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33211-2024 artfynd.xlsx
+++ b/artfynd/A 33211-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY83"/>
+  <dimension ref="A1:AZ83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237490</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237495</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810651</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810223</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131379057</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237457</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237484</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810050</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1615,6 +1660,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119808909</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1712,6 +1762,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119809044</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1809,6 +1864,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119808917</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1916,6 +1976,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237458</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2023,6 +2088,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237459</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2130,6 +2200,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237460</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2237,6 +2312,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237462</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2344,6 +2424,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237463</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2451,6 +2536,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237470</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2558,6 +2648,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237473</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2665,6 +2760,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237474</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2772,6 +2872,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237475</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2879,6 +2984,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237476</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2986,6 +3096,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237477</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3093,6 +3208,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237478</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3200,6 +3320,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237480</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3307,6 +3432,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237485</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3414,6 +3544,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237487</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3521,6 +3656,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237489</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3628,6 +3768,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237491</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3735,6 +3880,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237492</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3842,6 +3992,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237493</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3949,6 +4104,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237498</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4046,6 +4206,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119808918</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4143,6 +4308,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119808919</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4240,6 +4410,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119808923</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4337,6 +4512,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119808924</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4434,6 +4614,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119808930</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4531,6 +4716,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119808937</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4628,6 +4818,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119808938</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4725,6 +4920,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119809003</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4822,6 +5022,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119809028</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4919,6 +5124,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119809124</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5016,6 +5226,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119809202</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5113,6 +5328,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119809225</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5210,6 +5430,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810057</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5307,6 +5532,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810145</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5404,6 +5634,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810170</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5501,6 +5736,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810243</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5598,6 +5838,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810264</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5695,6 +5940,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810328</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5792,6 +6042,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810334</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5889,6 +6144,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810356</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5986,6 +6246,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810375</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6083,6 +6348,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810380</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6180,6 +6450,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810431</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6277,6 +6552,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810437</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6374,6 +6654,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810449</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6471,6 +6756,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810604</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6568,6 +6858,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810626</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6665,6 +6960,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810677</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6762,6 +7062,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810823</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6859,6 +7164,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810830</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6956,6 +7266,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810847</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7053,6 +7368,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810876</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7150,6 +7470,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810877</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7247,6 +7572,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810892</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7344,6 +7674,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810895</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7451,6 +7786,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237461</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7558,6 +7898,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237464</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7665,6 +8010,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237465</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7772,6 +8122,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237466</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7879,6 +8234,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237468</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7986,6 +8346,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237481</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8093,6 +8458,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237482</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8200,6 +8570,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237483</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8297,6 +8672,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810179</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8394,6 +8774,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810619</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8501,6 +8886,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237455</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8608,6 +8998,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237497</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8705,6 +9100,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119809326</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8812,6 +9212,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237456</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8919,6 +9324,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7237486</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9036,8 +9446,97 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119809838</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>